--- a/docs/anomalies_referentiel.xlsx
+++ b/docs/anomalies_referentiel.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corrections automatiques" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'À trancher'!$A$1:$L$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'À trancher'!$A$1:$L$129</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>267</v>
+        <v>209</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -777,27 +777,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>El103c</t>
+          <t>El174</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Si autre, préciser le contenu de l'offre concerné par l'exclusion (ex : prestation d'assurance)</t>
+          <t>Est-il prévu de mettre à disposition sur ugap.fr l'affichage du stock disponible ?</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>El103 : Si oui, préciser le contenu de l'offre concerné par l'exclusion (ex : prestation d'assurance)</t>
+          <t>El164a : Ce chapitre est-il applicable</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>La fille ne s'affiche que si la réponse à El103 contient « Autre », mais aucun choix de la liste ne correspond.</t>
+          <t>La fille ne s'affiche que si la réponse à El164a est égale à « Oui », mais aucun choix de la liste ne correspond.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Choix de El103 : Absence d'application de marge sur les taxes d'immatriculation | Surcoût Drom Com | Indeminité et annulation et modification de commande | Reprise de matériel</t>
+          <t>Choix de El164a : Oui, ce chapitre est applicable | Non,ce chapitre est non applicable</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Ajouter un choix « Autre » à la liste de El103, ou supprimer la règle</t>
+          <t>Passer l'opérateur à « contient » (le choix « Oui, ce chapitre est applicable » contient « Oui »)</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr"/>
@@ -829,27 +829,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>El174</t>
+          <t>El353b</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Est-il prévu de mettre à disposition sur ugap.fr l'affichage du stock disponible ?</t>
+          <t>Si oui, apporter la justification</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>El164a : Ce chapitre est-il applicable</t>
+          <t>El353 : Un minimum est-il imposé sur ce critère ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>La fille ne s'affiche que si la réponse à El164a est égale à « Oui », mais aucun choix de la liste ne correspond.</t>
+          <t>La fille ne s'affiche que si la réponse à El353 contient « Oui. Niveau minimal imposé », mais aucun choix de la liste ne correspond.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Choix de El164a : Oui, ce chapitre est applicable | Non,ce chapitre est non applicable</t>
+          <t>Choix de El353 : Non, Pas de niveau minimal imposé | Oui, Niveau minimal imposé</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Passer l'opérateur à « contient » (le choix « Oui, ce chapitre est applicable » contient « Oui »)</t>
+          <t>Remplacer le critère par « Oui, Niveau minimal imposé » (choix existant le plus proche)</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr"/>
@@ -881,27 +881,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>El332b</t>
+          <t>El361b</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Quelle est sa durée maximale et le délai de prévenance ?</t>
+          <t>Dans le cadre du guide vente préciser  les lot(s) concerné(s) ?</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>El332 : Une période de neutralisation des prestations (hors SAV) est-elle à prévoir ?</t>
+          <t>El361 : Le titulaire s'engage a fournir :</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>La fille ne s'affiche que si la réponse à El332 contient « Oui », mais aucun choix de la liste ne correspond.</t>
+          <t>La fille ne s'affiche que si la réponse à El361 contient « Guide de vente  », mais aucun choix de la liste ne correspond.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Choix de El332 : Non, aucune période de neutralisation | Période de congés | Changement de modèle | impact industriel lourd | Autre</t>
+          <t>Choix de El361 : Fiches technico-commerciales | Images numériques | Publipostages | Nuanciers | Banque de donnée de type AUTOCAD | Matériel de démonstration | Guide de vente | Non concerné pour l'offre</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Corriger le critère, ou ajouter le choix manquant à la liste de El332</t>
+          <t>Remplacer le critère par « Guide de vente » (choix existant le plus proche)</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr"/>
@@ -933,27 +933,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>El353b</t>
+          <t>El73b</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Si oui, apporter la justification</t>
+          <t>Si autre mode de multi attribution, préciser</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>El353 : Un minimum est-il imposé sur ce critère ?</t>
+          <t>El73 : Si AC BDC multi attribué ou mixte (Mono et multi attribué) préciser la modalité de multi attribution</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>La fille ne s'affiche que si la réponse à El353 contient « Oui. Niveau minimal imposé », mais aucun choix de la liste ne correspond.</t>
+          <t>La fille ne s'affiche que si la réponse à El73 contient « autre », mais aucun choix de la liste ne correspond.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Choix de El353 : Non, Pas de niveau minimal imposé | Oui, Niveau minimal imposé</t>
+          <t>Choix de El73 : Sur règle d’attribution définie au CCAP sur la base d’un questionnaire client ou d’une attestation de choix dérogatoire sans règle d’attribution à la défaillance, | Sur règle d’attribution définie au CCAP sur la base d’un questionnaire client ou d’une attestation de choix dérogatoire et d’une règle d’attribution à la défaillance | Sur règle d’attribution définie au CCAP sur la base de quantité minimale d’engagement au marché sans défaillance, | Sur règle d’attribution standard à la survenance du besoin et règle d’attribution à la défaillance | Sur règle d’attribution standard à la survenance du besoin sans règle d’attribution à la défaillance | Sur règle d'attribution à la défaillance temporaire et/ou définitive</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Remplacer le critère par « Oui, Niveau minimal imposé » (choix existant le plus proche)</t>
+          <t>Ajouter un choix « Autre » à la liste de El73, ou supprimer la règle</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Condition impossible</t>
+          <t>Condition orpheline</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -985,37 +985,33 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>El361b</t>
+          <t>El323</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Dans le cadre du guide vente préciser  les lot(s) concerné(s) ?</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>El361 : Le titulaire s'engage a fournir :</t>
-        </is>
-      </c>
+          <t>Si 1ère révision des prix, préciser la fréquence</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>La fille ne s'affiche que si la réponse à El361 contient « Guide de vente  », mais aucun choix de la liste ne correspond.</t>
+          <t>Règle « El323 dépend de El320 » : la question fille El323 n'existe pas dans le DCO.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Choix de El361 : Fiches technico-commerciales | images numériques | Publipostages | Nuanciers | Une banque de donnée de type AUTOCAD | Matériel de démonstration | Guide de vente</t>
+          <t>Libellé dans 100-Parametres : Si 1ère révision des prix, préciser la fréquence ; condition : &lt;&gt; « Oui »</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>La question fille ne s'affiche jamais quand on répond avec la liste.</t>
+          <t>Règle ignorée par l'outil.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Remplacer le critère par « Guide de vente » (choix existant le plus proche)</t>
+          <t>Supprimer la règle si la question a été retirée, sinon réintroduire la question</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr"/>
@@ -1027,7 +1023,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Condition impossible</t>
+          <t>Condition orpheline</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1037,37 +1033,33 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>El372</t>
+          <t>El323b</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Préciser la durée ?</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>El370 : Quelles sont les modalités de maintenance (préventive, corrective…) prévues ?</t>
-        </is>
-      </c>
+          <t>Si 1ère révision des prix, préciser le type de date applicable</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>La fille ne s'affiche que si la réponse à El370 contient « maintenance », mais aucun choix de la liste ne correspond.</t>
+          <t>Règle « El323b dépend de El320 » : la question fille El323b n'existe pas dans le DCO.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Choix de El370 : préventive | corrective/curative</t>
+          <t>Libellé dans 100-Parametres : Si 1ère révision des prix, préciser le type de date applicable ; condition : &lt;&gt; « Oui »</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>La question fille ne s'affiche jamais quand on répond avec la liste.</t>
+          <t>Règle ignorée par l'outil.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Corriger le critère, ou ajouter le choix manquant à la liste de El370</t>
+          <t>Supprimer la règle si la question a été retirée, sinon réintroduire la question</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr"/>
@@ -1079,7 +1071,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Condition impossible</t>
+          <t>Condition orpheline</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1089,37 +1081,33 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>El500</t>
+          <t>El323c</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Si autres, préciser la couverture géographique concernée</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>El59 : Préciser la couverture géographique à caractère obligatoire des matériels et/ou prestations à livrer ou exécuter par le…</t>
-        </is>
-      </c>
+          <t>Date à préciser</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>La fille ne s'affiche que si la réponse à El59 contient « Autres », mais aucun choix de la liste ne correspond.</t>
+          <t>Règle « El323c dépend de El320 » : la question fille El323c n'existe pas dans le DCO.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Choix de El59 : France métropolitaine | France continentale | Corse et îles littorales non desservies par un pont gratuit | DROM | COM | Etranger</t>
+          <t>Libellé dans 100-Parametres : Date à préciser ; condition : &lt;&gt; « Oui »</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>La question fille ne s'affiche jamais quand on répond avec la liste.</t>
+          <t>Règle ignorée par l'outil.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Ajouter un choix « Autre » à la liste de El59, ou supprimer la règle</t>
+          <t>Supprimer la règle si la question a été retirée, sinon réintroduire la question</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr"/>
@@ -1131,7 +1119,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Condition impossible</t>
+          <t>Condition orpheline</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1141,37 +1129,33 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>El60d</t>
+          <t>El335e</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Si autres, préciser la couverture géographique concernée</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>El60b : Si oui, préciser la couverture géographique à caractère facultatif des matériels et/ou prestations à livrer ou exécuter…</t>
-        </is>
-      </c>
+          <t>Quels sont les autres documents du marché?</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>La fille ne s'affiche que si la réponse à El60b contient « Autres », mais aucun choix de la liste ne correspond.</t>
+          <t>La question mère El335b n'existe pas dans le DCO.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Choix de El60b : France métropolitaine | France continentale | Corse et îles littorales non desservies par un pont gratuit | DROM | COM | Etranger</t>
+          <t>Condition : &lt;&gt; « Oui » ; libellé de la mère dans 100-Parametres : Y a-t-il des annexes au CCAP ?</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>La question fille ne s'affiche jamais quand on répond avec la liste.</t>
+          <t>Règle ignorée : la fille est toujours affichée.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Ajouter un choix « Autre » à la liste de El60b, ou supprimer la règle</t>
+          <t>Corriger l'identifiant de la mère (proches : El33b, El335) ou supprimer la règle</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr"/>
@@ -1183,43 +1167,47 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Condition orpheline</t>
+          <t>Plusieurs conditions</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>À trancher</t>
+          <t>À confirmer</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>El323</t>
+          <t>El178</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Si 1ère révision des prix, préciser la fréquence</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
+          <t>Si non, préciser les durées applicabes</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>El488, El177</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Règle « El323 dépend de El320 » : la question fille El323 n'existe pas dans le DCO.</t>
+          <t>2 conditions pour une même question (la règle d'administration n'en prévoit qu'une).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Libellé dans 100-Parametres : Si 1ère révision des prix, préciser la fréquence ; condition : &lt;&gt; « Oui »</t>
+          <t>El488 contient « non » ET El177 contient « Non »</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Règle ignorée par l'outil.</t>
+          <t>L'outil affiche la fille si TOUTES les conditions sont vraies (comme l'outil d'origine).</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Supprimer la règle si la question a été retirée, sinon réintroduire la question</t>
+          <t>Confirmer le « ET », ou indiquer si l'une des conditions suffit (« OU »)</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
@@ -1231,43 +1219,47 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Condition orpheline</t>
+          <t>Plusieurs conditions</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>À trancher</t>
+          <t>À confirmer</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>El323b</t>
+          <t>El179</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Si 1ère révision des prix, préciser le type de date applicable</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr"/>
+          <t>Si oui, préciser par qui elle est assurée</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>El488, El177</t>
+        </is>
+      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Règle « El323b dépend de El320 » : la question fille El323b n'existe pas dans le DCO.</t>
+          <t>2 conditions pour une même question (la règle d'administration n'en prévoit qu'une).</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Libellé dans 100-Parametres : Si 1ère révision des prix, préciser le type de date applicable ; condition : &lt;&gt; « Oui »</t>
+          <t>El488 contient « oui » ET El177 contient « Oui »</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Règle ignorée par l'outil.</t>
+          <t>L'outil affiche la fille si TOUTES les conditions sont vraies (comme l'outil d'origine).</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Supprimer la règle si la question a été retirée, sinon réintroduire la question</t>
+          <t>Confirmer le « ET », ou indiquer si l'une des conditions suffit (« OU »)</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr"/>
@@ -1279,43 +1271,47 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Condition orpheline</t>
+          <t>Plusieurs conditions</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>À trancher</t>
+          <t>À confirmer</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>El323c</t>
+          <t>El181</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Date à préciser</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
+          <t>Si non, préciser pour chaque lot la durée de cette garantie, les conditions de garantie</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>El180a, El445</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Règle « El323c dépend de El320 » : la question fille El323c n'existe pas dans le DCO.</t>
+          <t>2 conditions pour une même question (la règle d'administration n'en prévoit qu'une).</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Libellé dans 100-Parametres : Date à préciser ; condition : &lt;&gt; « Oui »</t>
+          <t>El180a contient « Non » ET El445 contient « Oui »</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Règle ignorée par l'outil.</t>
+          <t>L'outil affiche la fille si TOUTES les conditions sont vraies (comme l'outil d'origine).</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Supprimer la règle si la question a été retirée, sinon réintroduire la question</t>
+          <t>Confirmer le « ET », ou indiquer si l'une des conditions suffit (« OU »)</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr"/>
@@ -1327,43 +1323,47 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Condition orpheline</t>
+          <t>Plusieurs conditions</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>À trancher</t>
+          <t>À confirmer</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>El335e</t>
+          <t>El183</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Quels sont les autres documents du marché?</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr"/>
+          <t>Une fiche SAV est-elle exigée ?</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>El2, El445</t>
+        </is>
+      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>La question mère El335b n'existe pas dans le DCO.</t>
+          <t>2 conditions pour une même question (la règle d'administration n'en prévoit qu'une).</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Condition : &lt;&gt; « Oui » ; libellé de la mère dans 100-Parametres : Y a-t-il des annexes au CCAP ?</t>
+          <t>El2 contient « Matériel » ET El445 contient « Oui »</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Règle ignorée : la fille est toujours affichée.</t>
+          <t>L'outil affiche la fille si TOUTES les conditions sont vraies (comme l'outil d'origine).</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Corriger l'identifiant de la mère (proches : El33b, El335) ou supprimer la règle</t>
+          <t>Confirmer le « ET », ou indiquer si l'une des conditions suffit (« OU »)</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr"/>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>El178</t>
+          <t>El183b</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Si non, préciser les durées applicabes</t>
+          <t>Y-a-t-il une garantie de disponibilité du véhicule pour chaque véhicule immobilisé à cause d’une défaillance prise en charge au titre de la garantie ?</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>El488, El177</t>
+          <t>El0a, El393</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>El488 contient « non » ET El177 contient « Non »</t>
+          <t>El0a contient « véhicule » ET El393 contient « DAV »</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1437,17 +1437,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>El179</t>
+          <t>El183e</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Si oui, préciser par qui elle est assurée</t>
+          <t>Y-a-t-il une garantie de base d'autonomie de l'ensemble batterie ?</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>El488, El177</t>
+          <t>El393, El445</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>El488 contient « oui » ET El177 contient « Oui »</t>
+          <t>El393 contient « DAV » ET El445 contient « Oui »</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1489,17 +1489,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>El181</t>
+          <t>El191</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Si non, préciser pour chaque lot la durée de cette garantie, les conditions de garantie</t>
+          <t>Y-a t'il des produits en stock</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>El180a, El445</t>
+          <t>El2, El445</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>El180a contient « Non » ET El445 contient « Oui »</t>
+          <t>El2 contient « Matériel » ET El445 contient « Oui »</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>El183</t>
+          <t>El220</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Une fiche SAV est-elle exigée ?</t>
+          <t>S'il existe un surcoût, préciser lequel</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>El2, El445</t>
+          <t>El59, El60b</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>El2 contient « Matériel » ET El445 contient « Oui »</t>
+          <t>El59 contient « OM » ET El60b contient « OM »</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1593,17 +1593,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>El183b</t>
+          <t>El370</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Y-a-t-il une garantie de disponibilité du véhicule pour chaque véhicule immobilisé à cause d’une défaillance prise en charge au titre de la garantie ?</t>
+          <t>Quelles sont les modalités de maintenance (préventive, corrective…) prévues ?</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>El0a, El393</t>
+          <t>El134, El445</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>El0a contient « véhicule » ET El393 contient « DAV »</t>
+          <t>El134 contient « maintenance » ET El445 contient « Oui »</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1645,17 +1645,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>El183e</t>
+          <t>El500</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Y-a-t-il une garantie de base d'autonomie de l'ensemble batterie ?</t>
+          <t>Si autres, préciser la couverture géographique concernée</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>El393, El445</t>
+          <t>El59, El500c</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>El393 contient « DAV » ET El445 contient « Oui »</t>
+          <t>El59 contient « Autres » ET El500c contient « Autres »</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1697,17 +1697,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>El191</t>
+          <t>El60d</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Y-a t'il des produits en stock</t>
+          <t>Si autres, préciser la couverture géographique concernée</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>El2, El445</t>
+          <t>El60b, El60c</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>El2 contient « Matériel » ET El445 contient « Oui »</t>
+          <t>El60b contient « Autres » ET El60c contient « Autres »</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1749,17 +1749,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>El220</t>
+          <t>El78c</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>S'il existe un surcoût, préciser lequel</t>
+          <t>Dans le cadre de la passation de marchés subséquents sur AC non exécuté qui effectuera la remise en concurrence/la passation/la notification des marchés subséquents ?</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>El59, El60b</t>
+          <t>El71, El77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>El59 contient « OM » ET El60b contient « OM »</t>
+          <t>El71 contient « Marchés subséquents » ET El77 contient « Offre non exécutée »</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1801,17 +1801,17 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>El370</t>
+          <t>El78e</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Quelles sont les modalités de maintenance (préventive, corrective…) prévues ?</t>
+          <t>Quelles sont les modalités de passation des marchés subséquents ?</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>El134, El445</t>
+          <t>El71, El77</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>El134 contient « maintenance » ET El445 contient « Oui »</t>
+          <t>El71 contient « Marchés subséquents » ET El77 contient « Offre non exécutée »</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>El500</t>
+          <t>El78h</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Si autres, préciser la couverture géographique concernée</t>
+          <t>Quelles sont les modalités de passation des marchés subséquents ou de passation de bons de commandes ?</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>El59, El500c</t>
+          <t>El71, El77</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>El59 contient « Autres » ET El500c contient « Autres »</t>
+          <t>El71 contient « Marchés subséquents » ET El77 contient « Offre exécutée »</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1905,27 +1905,27 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>El60d</t>
+          <t>El78i</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Si autres, préciser la couverture géographique concernée</t>
+          <t>Quel est le volume estimé des marchés par an ?</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>El60b, El60c</t>
+          <t>El71, El77, El78h</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2 conditions pour une même question (la règle d'administration n'en prévoit qu'une).</t>
+          <t>3 conditions pour une même question (la règle d'administration n'en prévoit qu'une).</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>El60b contient « Autres » ET El60c contient « Autres »</t>
+          <t>El71 contient « Marchés subséquents » ET El77 contient « Offre exécutée » ET El78h contient « Marchés subséquents »</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1957,27 +1957,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>El78c</t>
+          <t>El78j</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Dans le cadre de la passation de marchés subséquents sur AC non exécuté qui effectuera la remise en concurrence/la passation/la notification des marchés subséquents ?</t>
+          <t>Quelle sera la forme des marchés subséquents</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>El71, El77</t>
+          <t>El71, El77, El78h</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2 conditions pour une même question (la règle d'administration n'en prévoit qu'une).</t>
+          <t>3 conditions pour une même question (la règle d'administration n'en prévoit qu'une).</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>El71 contient « Marchés subséquents » ET El77 contient « Offre non exécutée »</t>
+          <t>El71 contient « Marchés subséquents » ET El77 contient « Offre exécutée » ET El78h contient « Marchés subséquents »</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2009,17 +2009,17 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>El78e</t>
+          <t>ElTT502</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Quelles sont les modalités de passation des marchés subséquents ?</t>
+          <t>05.4.1 Typologie, prix et durée de la maintenance</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>El71, El77</t>
+          <t>El4, El445</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>El71 contient « Marchés subséquents » ET El77 contient « Offre non exécutée »</t>
+          <t>El4 contient « Oui » ET El445 contient « Oui »</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>El78h</t>
+          <t>ElTT503</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Quelles sont les modalités de passation des marchés subséquents ou de passation de bons de commandes ?</t>
+          <t>05.4.2 Commande de maintenance</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>El71, El77</t>
+          <t>El4, El445</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>El71 contient « Marchés subséquents » ET El77 contient « Offre exécutée »</t>
+          <t>El4 contient « Oui » ET El445 contient « Oui »</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -2103,47 +2103,39 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Plusieurs conditions</t>
+          <t>Marque conditionnante</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>À confirmer</t>
+          <t>À vérifier</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>El78i</t>
+          <t>El112b</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Quel est le volume estimé des marchés par an ?</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>El71, El77, El78h</t>
-        </is>
-      </c>
+          <t>Le marché prévoit-il une clause de devis tripartite ?</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3 conditions pour une même question (la règle d'administration n'en prévoit qu'une).</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>El71 contient « Marchés subséquents » ET El77 contient « Offre exécutée » ET El78h contient « Marchés subséquents »</t>
-        </is>
-      </c>
+          <t>Marquée « question conditionnante » (x) mais aucune règle ne dépend d'elle.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>L'outil affiche la fille si TOUTES les conditions sont vraies (comme l'outil d'origine).</t>
+          <t>Aucun (la marque n'est pas utilisée par le nouvel outil).</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Confirmer le « ET », ou indiquer si l'une des conditions suffit (« OU »)</t>
+          <t>Vérifier s'il manque une règle dans 100-Parametres ; sinon retirer la marque</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr"/>
@@ -2155,47 +2147,39 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Plusieurs conditions</t>
+          <t>Marque conditionnante</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>À confirmer</t>
+          <t>À vérifier</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>El78j</t>
+          <t>El112c</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Quelle sera la forme des marchés subséquents</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>El71, El77, El78h</t>
-        </is>
-      </c>
+          <t>Si autre, en préciser la raison</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3 conditions pour une même question (la règle d'administration n'en prévoit qu'une).</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>El71 contient « Marchés subséquents » ET El77 contient « Offre exécutée » ET El78h contient « Marchés subséquents »</t>
-        </is>
-      </c>
+          <t>Marquée « question conditionnante » (x) mais aucune règle ne dépend d'elle.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>L'outil affiche la fille si TOUTES les conditions sont vraies (comme l'outil d'origine).</t>
+          <t>Aucun (la marque n'est pas utilisée par le nouvel outil).</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Confirmer le « ET », ou indiquer si l'une des conditions suffit (« OU »)</t>
+          <t>Vérifier s'il manque une règle dans 100-Parametres ; sinon retirer la marque</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr"/>
@@ -2207,47 +2191,39 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Plusieurs conditions</t>
+          <t>Marque conditionnante</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>À confirmer</t>
+          <t>À vérifier</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>ElTT502</t>
+          <t>El180</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>05.4.1 Typologie, prix et durée de la maintenance</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>El4, El445</t>
-        </is>
-      </c>
+          <t>Si oui, préciser le détail de la garantie</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2 conditions pour une même question (la règle d'administration n'en prévoit qu'une).</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>El4 contient « Oui » ET El445 contient « Oui »</t>
-        </is>
-      </c>
+          <t>Marquée « question conditionnante » (x) mais aucune règle ne dépend d'elle.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>L'outil affiche la fille si TOUTES les conditions sont vraies (comme l'outil d'origine).</t>
+          <t>Aucun (la marque n'est pas utilisée par le nouvel outil).</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Confirmer le « ET », ou indiquer si l'une des conditions suffit (« OU »)</t>
+          <t>Vérifier s'il manque une règle dans 100-Parametres ; sinon retirer la marque</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr"/>
@@ -2259,47 +2235,39 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Plusieurs conditions</t>
+          <t>Marque conditionnante</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>À confirmer</t>
+          <t>À vérifier</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>ElTT503</t>
+          <t>El200</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>05.4.2 Commande de maintenance</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>El4, El445</t>
-        </is>
-      </c>
+          <t>Une clause de performance est-elle prévue ?</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2 conditions pour une même question (la règle d'administration n'en prévoit qu'une).</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>El4 contient « Oui » ET El445 contient « Oui »</t>
-        </is>
-      </c>
+          <t>Marquée « question conditionnante » (x) mais aucune règle ne dépend d'elle.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>L'outil affiche la fille si TOUTES les conditions sont vraies (comme l'outil d'origine).</t>
+          <t>Aucun (la marque n'est pas utilisée par le nouvel outil).</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Confirmer le « ET », ou indiquer si l'une des conditions suffit (« OU »)</t>
+          <t>Vérifier s'il manque une règle dans 100-Parametres ; sinon retirer la marque</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
@@ -2321,12 +2289,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>El112b</t>
+          <t>El2b</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Le marché prévoit-il une clause de devis tripartite ?</t>
+          <t>Si prestations, préciser leur nature</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
@@ -2365,12 +2333,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>El112c</t>
+          <t>El317a</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Si autre, en préciser la raison</t>
+          <t>Le surcoût outre-mer peut-il varier?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
@@ -2409,12 +2377,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>El180</t>
+          <t>El338</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Si oui, préciser le détail de la garantie</t>
+          <t>Pour les offres de produits, la réalisation d'une recette technique réalisée par l'UGAP est-elle envisagée ?</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
@@ -2453,12 +2421,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>El200</t>
+          <t>El394</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Une clause de performance est-elle prévue ?</t>
+          <t>Univers (standard d'univers)</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
@@ -2497,12 +2465,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>El2b</t>
+          <t>El44</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Si prestations, préciser leur nature</t>
+          <t>Si oui à la commercialisation sur le WEB, Un contrôle/accès restreint à typologie de clients/utilisateurs chez le client est-il en place ?</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
@@ -2541,12 +2509,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>El317a</t>
+          <t>El500</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Le surcoût outre-mer peut-il varier?</t>
+          <t>Si autres, préciser la couverture géographique concernée</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
@@ -2585,12 +2553,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>El338</t>
+          <t>El511</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Pour les offres de produits, la réalisation d'une recette technique réalisée par l'UGAP est-elle envisagée ?</t>
+          <t>Le montant total estimé de la procédure est-il supérieur à 250 millions d'euros HT ?</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
@@ -2629,29 +2597,33 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>El394</t>
+          <t>El60c</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Univers (standard d'univers)</t>
+          <t>Si couverture géographique facultative à l'étranger, l'étranger comprend</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Marquée « question conditionnante » (x) mais aucune règle ne dépend d'elle.</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr"/>
+          <t>Question mère d'au moins une règle, mais non marquée « conditionnante ».</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Filles : El60d</t>
+        </is>
+      </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Aucun (la marque n'est pas utilisée par le nouvel outil).</t>
+          <t>Aucun (le nouvel outil se base sur les règles).</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Vérifier s'il manque une règle dans 100-Parametres ; sinon retirer la marque</t>
+          <t>Ajouter la marque (cohérence de la base)</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr"/>
@@ -2673,12 +2645,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>El44</t>
+          <t>El82</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Si oui à la commercialisation sur le WEB, Un contrôle/accès restreint à typologie de clients/utilisateurs chez le client est-il en place ?</t>
+          <t>Des travaux d'interfacage ou de déploiement long sont-ils prévus nécessitant des échanges avec le titulaire avant ouverture du marché à la commercialisation ?</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
@@ -2717,12 +2689,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>El500</t>
+          <t>El85b</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Si autres, préciser la couverture géographique concernée</t>
+          <t>Si oui, expliquer les modalités de reconduction ?</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
@@ -2751,7 +2723,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Marque conditionnante</t>
+          <t>Liste de choix</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2761,29 +2733,34 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>El511</t>
+          <t>El0a</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Le montant total estimé de la procédure est-il supérieur à 250 millions d'euros HT ?</t>
+          <t>Cette procédure est-elle concernée par une des définitions suivantes et si oui sélectionner les définitions concernées :</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Marquée « question conditionnante » (x) mais aucune règle ne dépend d'elle.</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
+          <t>La liste nommée ListeEl0a (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : Ensemble batterie | Location de batterie | Acquisition de batterie | Piles à combustibles (hydrogène) | Acquisition de véhicules | Acquisition de véhicules à hydrogène | Acquisition de véhicules 100% électriques | Acquisition d'équipement de véhicules | Location de véhicules | Réservoirs à hydrogène | Non concerné pour l'offre
+Texte : Ensemble batterie | Location de batterie | Acquisition de batterie | Piles à combustibles (hydrogène) | Acquisition de véhicules | Acquisition de véhicules à hydrogène | Acquisition de véhicules 100% électriques | Acquisition d'équipement de véhicules | Location de véhicules</t>
+        </is>
+      </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Aucun (la marque n'est pas utilisée par le nouvel outil).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Vérifier s'il manque une règle dans 100-Parametres ; sinon retirer la marque</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr"/>
@@ -2795,7 +2772,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Marque conditionnante</t>
+          <t>Liste de choix</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2805,33 +2782,34 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>El60c</t>
+          <t>El103</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Si couverture géographique facultative à l'étranger, l'étranger comprend</t>
+          <t>Si oui, préciser le contenu de l'offre concerné par l'exclusion (ex : prestation d'assurance)</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Question mère d'au moins une règle, mais non marquée « conditionnante ».</t>
+          <t>La liste nommée ListeEl103 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Filles : El60d</t>
+          <t>Liste proposée : Absence d'application de marge sur les taxes d'immatriculation | Surcoût Drom Com | Indeminité et annulation et modification de commande | Reprise de matériel | Autre
+Texte : Absence d'application de marge sur les taxes d'immatriculation | Surcoût Drom Com | Indeminité et annulation et modification de commande | Reprise de matériel</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Aucun (le nouvel outil se base sur les règles).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Ajouter la marque (cohérence de la base)</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr"/>
@@ -2843,7 +2821,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Marque conditionnante</t>
+          <t>Liste de choix</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2853,29 +2831,34 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>El82</t>
+          <t>El107</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Des travaux d'interfacage ou de déploiement long sont-ils prévus nécessitant des échanges avec le titulaire avant ouverture du marché à la commercialisation ?</t>
+          <t>Si clause promotionnelle applicable, quel est le périmètre applicable ?</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Marquée « question conditionnante » (x) mais aucune règle ne dépend d'elle.</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr"/>
+          <t>La liste nommée ListeEl107 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : Diminution du prix net d'un ou de plusieurs matériel(s)/prestations | Mise en place de conditionnements promotionnels (vente de lots) | Mise en place de packages dit promotionnels regroupant plusieurs matériels, options, accessoires du marché
+Texte : Diminution du prix net d'un ou de plusieurs matériel(s)/prestations | La mise en place de conditionnements promotionnels (vente de lots) | La mise en place de packages dit promotionnels regroupant plusieurs matériels, options, accessoires du marché</t>
+        </is>
+      </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Aucun (la marque n'est pas utilisée par le nouvel outil).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Vérifier s'il manque une règle dans 100-Parametres ; sinon retirer la marque</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr"/>
@@ -2887,7 +2870,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Marque conditionnante</t>
+          <t>Liste de choix</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2897,29 +2880,34 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>El85b</t>
+          <t>El111</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Si oui, expliquer les modalités de reconduction ?</t>
+          <t>Si oui, préciser lesquels</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Marquée « question conditionnante » (x) mais aucune règle ne dépend d'elle.</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr"/>
+          <t>La liste nommée ListeEl111 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : Qualification du besoin par le titulaire et rédaction d'un dossier technique le cas échéant | Fiche de vente | Prévisite du titulaire | Questionnaire client (offre plurielle) | Fiche de recensement | Eprocurement | Attestation de complément de parc | Devis tripartite avec outillage | Convention d'embarquement | Autre
+Texte : Qualification du besoin par le titulaire et rédaction d’un dossier technique le cas échéant | fiche de vente | prévisite du titulaire | questionnaire client (offre plurielle) | fiche de recensement | attestation de complément de parc | eprocurement | devis tripartite avec outillage | convention d'embarquement | autre</t>
+        </is>
+      </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Aucun (la marque n'est pas utilisée par le nouvel outil).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Vérifier s'il manque une règle dans 100-Parametres ; sinon retirer la marque</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr"/>
@@ -2941,34 +2929,34 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>El132</t>
+          <t>El114</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Quelle est la fréquence d'émission des bons de commandes ?</t>
+          <t>Si non, préciser lesquels</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+          <t>La liste nommée ListeEl114 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : A la survenance du besoin | A échéance (mensuelle | trimestrielle | annuelle) | autre ou mixte
-Texte : A la survenance du besoin | A échéance (mensuelle, trimestrielle, annuelle) | autre ou mixte</t>
+          <t>Liste proposée : Devis tripartite | CCM | E-commerce | Réel constaté | Autre
+Texte : Devis tripartite / CCM / E-commerce / réel constaté /Autre</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
@@ -2990,34 +2978,34 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>El138</t>
+          <t>El123</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>En cas d’annulation/modification des bons de Commande client existe-t-il une dérogation aux CGV (=annulation le jour même)?</t>
+          <t>Si non, préciser les modalités particulières applicables</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+          <t>La liste nommée ListeEl123 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui, la règle d'annulation/modification ou annulation déroge aux CGV | Non, la règle d'annulation/modification ou annulation est conforme aux CGV
-Texte : Oui, la règle d'annulation/modification ou annulation déroge aux CGV | Non,la règle d'annulation/modification ou annulation est conforme aux CGV</t>
+          <t>Liste proposée : Devis tripartite | CCM | E-commerce | Réel constaté | Canal 4 | Autre
+Texte : Devis tripartite | CCM | E-commerce | réel constaté | Autre</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr"/>
@@ -3039,12 +3027,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>El142</t>
+          <t>El132</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Minimum d’achat est-il applicable pour exonérer des frais de port est-il prévu / envisagé</t>
+          <t>Quelle est la fréquence d'émission des bons de commandes ?</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -3055,18 +3043,18 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui, minimum d'achat pour l'exonération des frais de port | Non, absence de minimum d'achat pour l'exonération des frais de port
-Texte : Oui, minimum d'achat pour l'exonération des frais de port | Non,Absence de minimum d'achat pour l'exonération des frais de port</t>
+          <t>Liste proposée : A la survenance du besoin | A échéance (mensuelle | trimestrielle | annuelle) | autre ou mixte
+Texte : A la survenance du besoin | A échéance (mensuelle, trimestrielle, annuelle) | autre ou mixte</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr"/>
@@ -3088,34 +3076,34 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>El151b</t>
+          <t>El132b</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Si oui, en préciser le type d'échéance</t>
+          <t>En cas de BDC à échéance, préciser s'il s'agit d'une mono, multi échéance et pour quelle échéance l'UGAP émet-elle une commande ? (mensuelle, trimestrielle, semestrielle ou annuelle)</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+          <t>La liste nommée ListeEl132b (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Mono échéance | Multi échéance | Mono échéance &amp; Multi échéance
-Texte : Mono échéance | Multi échéance | Mixte (Mono et Multi échéance)</t>
+          <t>Liste proposée : Mensuelle | Trimestrielle | Semestrielle | Annuelle
+Texte : mensuelle,trimestrielle,semestrielle | annuelle</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr"/>
@@ -3137,34 +3125,34 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>El152</t>
+          <t>El134</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Si mono échéance, en préciser le terme applicable</t>
+          <t>Quelles sont les typologies de commande de maintenance?</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+          <t>La liste nommée ListeEl134 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Terme échoir | Terme échu | Non concerné pour l'offre
-Texte : Terme échoir | Terme échu | Multi terme (échu et échoir)</t>
+          <t>Liste proposée : Location maintenance | Acquisition maintenance | Maintenance Full service | Non concerné pour l'offre
+Texte : Location maintenance | Acquisition maintenance | Full service | Non concerné pour l'offre</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr"/>
@@ -3186,12 +3174,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>El152b</t>
+          <t>El138</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Si multi échéance, en préciser le terme applicable</t>
+          <t>En cas d’annulation/modification des bons de Commande client existe-t-il une dérogation aux CGV (=annulation le jour même)?</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
@@ -3202,18 +3190,18 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Terme échoir | Terme échu | Non concerné pour l'offre
-Texte : Terme échoir | Terme échu | Multi terme (échu et échoir)</t>
+          <t>Liste proposée : Oui, la règle d'annulation/modification ou annulation déroge aux CGV | Non, la règle d'annulation/modification ou annulation est conforme aux CGV
+Texte : Oui, la règle d'annulation/modification ou annulation déroge aux CGV | Non,la règle d'annulation/modification ou annulation est conforme aux CGV</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr"/>
@@ -3235,12 +3223,12 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>El161c</t>
+          <t>El142</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Si non, indiquer le pourcentage</t>
+          <t>Minimum d’achat est-il applicable pour exonérer des frais de port est-il prévu / envisagé</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
@@ -3251,18 +3239,18 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : 30% | 60% | 70%
-Texte : Champ libre</t>
+          <t>Liste proposée : Oui, minimum d'achat pour l'exonération des frais de port | Non, absence de minimum d'achat pour l'exonération des frais de port
+Texte : Oui, minimum d'achat pour l'exonération des frais de port | Non,Absence de minimum d'achat pour l'exonération des frais de port</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr"/>
@@ -3284,12 +3272,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>El163</t>
+          <t>El151b</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Si oui, est-il conforme au standard: - Montant est supérieur à 50 K€ - Délai de la prestation est supérieur à 90 jours  - Montant d'acompte fixé au maximum à 40% du montant TTC du BDC?</t>
+          <t>Si oui, en préciser le type d'échéance</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
@@ -3300,18 +3288,18 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Acompte conforme au standard dont le montant est supérieur à 50 000 euros | dont le délai de prestation est supérieur à 90 jours | Maximum 40% | Garantie à première demande | Acompte non conforme au standard
-Texte : Acompte conforme au standard dont le montant est supérieur à 50 000 euros, dont le délai de prestation est supérieur à 90 jours, Maximum 40%, Garantie à première demande | Acompte non conforme au standard</t>
+          <t>Liste proposée : Mono échéance | Multi échéance | Mono échéance &amp; Multi échéance
+Texte : Mono échéance | Multi échéance | Mixte (Mono et Multi échéance)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr"/>
@@ -3333,12 +3321,12 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>El183b</t>
+          <t>El152</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Y-a-t-il une garantie de disponibilité du véhicule pour chaque véhicule immobilisé à cause d’une défaillance prise en charge au titre de la garantie ?</t>
+          <t>Si mono échéance, en préciser le terme applicable</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
@@ -3349,18 +3337,18 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui, existence d'une garantie de disponibilité | Non, absence de garantie de disponibilité
-Texte : Non, absence de garantie de disponibilité | Oui, existence d'une garantie de disponibilité</t>
+          <t>Liste proposée : Terme échoir | Terme échu | Non concerné pour l'offre
+Texte : Terme échoir | Terme échu | Multi terme (échu et échoir)</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr"/>
@@ -3382,12 +3370,12 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>El183e</t>
+          <t>El152b</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Y-a-t-il une garantie de base d'autonomie de l'ensemble batterie ?</t>
+          <t>Si multi échéance, en préciser le terme applicable</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
@@ -3398,18 +3386,18 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui | existence d'une garantie autonomie de l'ensemble batterie | Non | absence de garantie autonomie de l'ensemble batterie
-Texte : Oui, Existence d'une garantie autonomie de l'ensemble batterie | Non, Absence de garantie autonomie de l'ensemble batterie</t>
+          <t>Liste proposée : Terme échoir | Terme échu | Non concerné pour l'offre
+Texte : Terme échoir | Terme échu | Multi terme (échu et échoir)</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr"/>
@@ -3431,12 +3419,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>El183j</t>
+          <t>El161c</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Si oui, quel est le délai correspondant après la fin de la fabrication du dernier matériel  ?</t>
+          <t>Si non, indiquer le pourcentage</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -3447,18 +3435,18 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : 5 ans | Autre
-Texte : 5 ans | 10 ans | autre | Non concerné pour l'offre</t>
+          <t>Liste proposée : 30% | 60% | 70%
+Texte : Champ libre</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr"/>
@@ -3480,12 +3468,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>El183l</t>
+          <t>El163</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Y-a-t-il une garantie minimum de base du véhicule complet hors batterie ?</t>
+          <t>Si oui, est-il conforme au standard: - Montant est supérieur à 50 K€ - Délai de la prestation est supérieur à 90 jours  - Montant d'acompte fixé au maximum à 40% du montant TTC du BDC?</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
@@ -3496,18 +3484,18 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui, existence d'une garantie minimum de base du véhicule complet hors batterie | Non, absence de garantie minimum de base du véhicule complet hors batterie
-Texte : Non, absence de garantie minimum de base du véhicule complet hors batterie | Oui, existence d'une garantie minimum de base du véhicule complet hors batterie</t>
+          <t>Liste proposée : Acompte conforme au standard dont le montant est supérieur à 50 000 euros | dont le délai de prestation est supérieur à 90 jours | Maximum 40% | Garantie à première demande | Acompte non conforme au standard
+Texte : Acompte conforme au standard dont le montant est supérieur à 50 000 euros, dont le délai de prestation est supérieur à 90 jours, Maximum 40%, Garantie à première demande | Acompte non conforme au standard</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr"/>
@@ -3529,34 +3517,34 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>El184</t>
+          <t>El173</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Une extension de garantie doit-elle être mise en place ?</t>
+          <t>Quelles sont les modalités de livraison (hors France métropolitaine)</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+          <t>La liste nommée ListeEl173 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui | une extension de garantie doit être mise en place | Non | absence d'extension de garantie
-Texte : Oui, une extension de garantie doit être mise en place | Non, absence d'extension de garantie</t>
+          <t>Liste proposée : Chez un concessionnaire ou lieu de gardiennage | Chez le client (sans emballage) | Chez le transitaire du bénéficiaire en France métropolitaine | sur le site du bénéficiaire avec prise en charge des frais d'emballage de transport et de dédouanement
+Texte : Chez le transitaire du bénéficiaire en France Métropolitaine | Sur le site du bénéficiaire avec prise en charge des frais d'emballage de transport et de dédouanement</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr"/>
@@ -3578,34 +3566,34 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>El185</t>
+          <t>El179</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Si oui, concerne t'elle un matériel référencé  par le titulaire auprès du constructeur ?</t>
+          <t>Si oui, préciser par qui elle est assurée</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+          <t>La liste nommée ListeEl179 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Non, elle ne concerne pas du matériel référencé au prix renseigné par le titulaire | Oui, elle concerne du matériel référencé au prix proposé par le titulaire
-Texte : Oui, elle concerne du matériel référencé au prix proposé par le titulaire | Non, elle ne concerne pas du matériel référencé au prix renseigné par le titulaire</t>
+          <t>Liste proposée : Titulaire | Constructeur | Tiers | Non concerné pour l'offre
+Texte : Titulaire/Constructeur/Tiers</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr"/>
@@ -3627,34 +3615,34 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>El186</t>
+          <t>El181b</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Si oui, s'agit-il d'une extension de garantie contrôlée ?</t>
+          <t>Quelles sont les conditions de garantie ?</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+          <t>La liste nommée ListeEl181b (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui | Extension de garantie contrôlée | Non | absence d'extension de garantie contrôlée
-Texte : Oui, Extension de garantie contrôlée | Non, absence d'extension de garantie contrôlée</t>
+          <t>Liste proposée : Sur les lieux d'utilisation du matériel | Sur site bénéficiare | Sur site ou en retour atelier (frais logistiques A/R à la charge du titulaire) | Chez le titulaire ou tiers (agent, concessionnaire, distributeur…) | A distance (logiciel)
+Texte : Sur site client | Sur les lieux d'utilisation du matériel | Sur site bénéficiaire | Sur site ou en retour atelier (frais logistiques A/R à la charge du titulaire), chez le titulaire ou tiers (agent, concessionnaire, distributeur…), à distance (logiciel)</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr"/>
@@ -3676,12 +3664,12 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>El191</t>
+          <t>El183b</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Y-a t'il des produits en stock</t>
+          <t>Y-a-t-il une garantie de disponibilité du véhicule pour chaque véhicule immobilisé à cause d’une défaillance prise en charge au titre de la garantie ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
@@ -3692,18 +3680,18 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui, Existence de produits en stock | Non, Absence de produits en stock
-Texte : Non, Absence de produits en stock | Oui, Existence de produits en stock</t>
+          <t>Liste proposée : Oui, existence d'une garantie de disponibilité | Non, absence de garantie de disponibilité
+Texte : Non, absence de garantie de disponibilité | Oui, existence d'une garantie de disponibilité</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr"/>
@@ -3725,12 +3713,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>El199b</t>
+          <t>El183e</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Le plafond des pénalités est-il conforme au standard établi?</t>
+          <t>Y-a-t-il une garantie de base d'autonomie de l'ensemble batterie ?</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
@@ -3741,18 +3729,18 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui, le plafond des pénalités est conforme au standard de 30% du bon de commande HT | Non, le plafond des pénalités est dérogatoire au standard établi
-Texte : Oui, le plafond des pénalités est conforme au standard établi | Non, le plafond des pénalités est dérogatoire au standard établi</t>
+          <t>Liste proposée : Oui | existence d'une garantie autonomie de l'ensemble batterie | Non | absence de garantie autonomie de l'ensemble batterie
+Texte : Oui, Existence d'une garantie autonomie de l'ensemble batterie | Non, Absence de garantie autonomie de l'ensemble batterie</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr"/>
@@ -3774,12 +3762,12 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>El222</t>
+          <t>El183j</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>De quelle façon s'exprime le surcoût étranger ?</t>
+          <t>Si oui, quel est le délai correspondant après la fin de la fabrication du dernier matériel  ?</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
@@ -3790,18 +3778,18 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui | Non
-Texte : sur devis | en pourcentage</t>
+          <t>Liste proposée : 5 ans | Autre
+Texte : 5 ans | 10 ans | autre | Non concerné pour l'offre</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr"/>
@@ -3823,12 +3811,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>El224a</t>
+          <t>El183l</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Si oui préciser si elles sont liées à des prestations locales</t>
+          <t>Y-a-t-il une garantie minimum de base du véhicule complet hors batterie ?</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
@@ -3839,18 +3827,18 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui | Non
-Texte : Prestation locale hors France Métropolitaine (TVA 0%) | Prestation locale hors France Métropolitaine (TVA 8,5%) | Prestation locale DROM/COM (TVA Achat 20%_Vente 8,5%)</t>
+          <t>Liste proposée : Oui, existence d'une garantie minimum de base du véhicule complet hors batterie | Non, absence de garantie minimum de base du véhicule complet hors batterie
+Texte : Non, absence de garantie minimum de base du véhicule complet hors batterie | Oui, existence d'une garantie minimum de base du véhicule complet hors batterie</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr"/>
@@ -3872,12 +3860,12 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>El224c</t>
+          <t>El184</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Si oui préciser si elles concernent les frais de transport</t>
+          <t>Une extension de garantie doit-elle être mise en place ?</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
@@ -3888,18 +3876,18 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui | Non
-Texte : Frais de transport, pour les livraisons hors France Métropolitaine (TVA 0%) | Frais de transport, pour les livraisons hors France Métropolitaine (TVA 8,5%) | Frais de transport, pour les livraisons hors France Métropolitaine (TVA 20%)</t>
+          <t>Liste proposée : Oui | une extension de garantie doit être mise en place | Non | absence d'extension de garantie
+Texte : Oui, une extension de garantie doit être mise en place | Non, absence d'extension de garantie</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr"/>
@@ -3921,12 +3909,12 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>El224d</t>
+          <t>El185</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Si oui préciser si elles concernent l'assurance livraison</t>
+          <t>Si oui, concerne t'elle un matériel référencé  par le titulaire auprès du constructeur ?</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
@@ -3937,18 +3925,18 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui | Assurance pour les livraisons hors France Métropolitaine (TVA 0%) | Non | Absence d'assurance pour la livraison
-Texte : Oui, Assurance pour les livraisons hors France Métropolitaine (TVA 0%) | Non, Absence d'assurance pour la livraison</t>
+          <t>Liste proposée : Non, elle ne concerne pas du matériel référencé au prix renseigné par le titulaire | Oui, elle concerne du matériel référencé au prix proposé par le titulaire
+Texte : Oui, elle concerne du matériel référencé au prix proposé par le titulaire | Non, elle ne concerne pas du matériel référencé au prix renseigné par le titulaire</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr"/>
@@ -3970,12 +3958,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>El258c</t>
+          <t>El186</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'offre inclut-elle des exigences en matière d'impact environnemental du transport?</t>
+          <t>Si oui, s'agit-il d'une extension de garantie contrôlée ?</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
@@ -3986,18 +3974,18 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui, l'offre inclut des exigences en matière d'impact environnemental du transport | Non, l'offre n'inclut pas d'exigences en matière d'impact environnemental du transport
-Texte : Oui, l'offre inclut des exigences en matière d'impact environnemental du transport | Oui, l'offre n'inclut pas d'exigences en matière d'impact environnemental du transport</t>
+          <t>Liste proposée : Oui | Extension de garantie contrôlée | Non | absence d'extension de garantie contrôlée
+Texte : Oui, Extension de garantie contrôlée | Non, absence d'extension de garantie contrôlée</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr"/>
@@ -4019,12 +4007,12 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>El260a</t>
+          <t>El191</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Les produits issus du réemploi/réutilisation sont-ils intégrés dans l'offre (exemple : architecture lot dédié, facultatif libre ...)?</t>
+          <t>Y-a t'il des produits en stock</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
@@ -4035,18 +4023,18 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui, l'offre/les lots intègre(nt) des produits issus du réemploi/réutilisation | Non, l'offre n'intègre pas des produits issus du réemploi/réutilisation
-Texte : Oui, l'offre intègre des produits issus du réemploi/réutilisation | Non, l'offre n'intègre pas des produits issus du réemploi/réutilisation</t>
+          <t>Liste proposée : Oui, Existence de produits en stock | Non, Absence de produits en stock
+Texte : Non, Absence de produits en stock | Oui, Existence de produits en stock</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr"/>
@@ -4068,12 +4056,12 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>El260b</t>
+          <t>El199b</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Une obligation imposant aux fournisseurs de remettre pendant l'exécution du marché l'information sur l'intégration de matière recyclée dans les produits est-elle bien intégrée pour les lots le nécessitant (produits textiles, consommables d'impression, papier, engins de transports...)?</t>
+          <t>Le plafond des pénalités est-il conforme au standard établi?</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
@@ -4084,18 +4072,18 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui, l'offre/les lots prévoi(en)t pour le titulaire l'obligation de remettre pendant l'exécution du marché ces informations | Non, l'offre ne prévoit pas la remise de ces informations
-Texte : Oui, l'offre prévoit pour le titulaire l'obligation de remettre pendant l'exécution du marché ces informations | Non, l'offre ne prévoit pas la remise de ces informations</t>
+          <t>Liste proposée : Oui, le plafond des pénalités est conforme au standard de 30% du bon de commande HT | Non, le plafond des pénalités est dérogatoire au standard établi
+Texte : Oui, le plafond des pénalités est conforme au standard établi | Non, le plafond des pénalités est dérogatoire au standard établi</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr"/>
@@ -4117,34 +4105,34 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>El260g</t>
+          <t>El206b</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Les lots prévoient-ils une traçabilité sociale des chaines d'approvisionnement ?</t>
+          <t>Si autre, indiquer les indicateurs envisager pour suivre l'exécution (en cas de sélection autre, saisir directement les indicateurs en texte libre)</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+          <t>La liste nommée ListeEl206b (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui, traçabilité sociale des chaines d'approvisionnement pour tous les lots des univers concernés | Non, pas de traçabilité sociale des chaines d'approvisionnement pour tous les lots des univers concernés
-Texte : Oui, traçabilité sociale des chaines d'approvisionnement pour tous les lots des univers concernés | Non, pas de traçabilité sociale des chaines d'approvisionnement pour tous les lots des univers concernés.</t>
+          <t>Liste proposée : Nb fichiers traçabilité traités | Délai transmission fichiers  traçabilité | Tx d prise en compte des commande | Fiabilité livraison prév. | Fiabilité date livraison prév. | Conformité facturation fournisseur | Tx prise en charge des commentaires | Taux litiges résolus
+Texte : Nb fichiers traçabilité traités | Délai transmission fichiers  traçabilité | Tx d prise en compte des commande | Fiabilité livraison prév. | Fiabilité date livraison prév. | Conformité facturation fournisseur | Tx prise en charge des commentaires | Taux litiges résolus / Ou texte libre</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr"/>
@@ -4166,34 +4154,34 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>El268</t>
+          <t>El220</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Si oui, à compter de quel délai le titulaire s'engage à communiquer au bénéficiaire le droit d'utilisation des logiciels concédés ?  (si délai autre que le choix sur liste, saisir directement le délai dans la réponse)</t>
+          <t>S'il existe un surcoût, préciser lequel</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+          <t>La liste nommée ListeEl220 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Dans un délai de 30 jours | Dans un délai de 7 jours
-Texte : Champ libre</t>
+          <t>Liste proposée : Surcoût corse | Surcoût outre-mer
+Texte : Oui, surcoût outre-mer | Non, Absence de surcoût outre-mer</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr"/>
@@ -4215,12 +4203,12 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>El270</t>
+          <t>El222</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>L'offre antérieure affiche-t'elle un stock fournisseur  ?</t>
+          <t>De quelle façon s'exprime le surcoût étranger ?</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
@@ -4231,18 +4219,18 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui | l'offre antérieure affiche un stock fournisseur | Non | l'offre antérieure n'affiche pas de stock fournisseur
-Texte : Oui, l'offre antérieure affiche un stock fournisseur | Non, l'offre antérieure n'affiche pas de stock fournisseur</t>
+          <t>Liste proposée : Oui | Non
+Texte : sur devis | en pourcentage</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr"/>
@@ -4264,12 +4252,12 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>El302</t>
+          <t>El224a</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Le principe d'engagement maximum sans minimum s'applique-t 'il ?</t>
+          <t>Si oui préciser si elles sont liées à des prestations locales</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
@@ -4280,18 +4268,18 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui, le principe d'engagement maximum sans minimum s'applique | Non, dérogation au standard
-Texte : Oui, le principe d'engagement maximum avec montants estimés s'applique | Non, dérogation au standard</t>
+          <t>Liste proposée : Oui | Non
+Texte : Prestation locale hors France Métropolitaine (TVA 0%) | Prestation locale hors France Métropolitaine (TVA 8,5%) | Prestation locale DROM/COM (TVA Achat 20%_Vente 8,5%)</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr"/>
@@ -4313,12 +4301,12 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>El30b</t>
+          <t>El224c</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>l'UGAP est-elle bénéficiaire ?</t>
+          <t>Si oui préciser si elles concernent les frais de transport</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
@@ -4329,18 +4317,18 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui, l'UGAP est bénéficaire de l'offre | Non, l'UGAP n'est pas bénéficiaire de l'offre
-Texte : Oui, l'UGAP est bénéficiaire de l'offre | Non, l'UGAP n'est pas bénéficiaire de l'offre</t>
+          <t>Liste proposée : Oui | Non
+Texte : Frais de transport, pour les livraisons hors France Métropolitaine (TVA 0%) | Frais de transport, pour les livraisons hors France Métropolitaine (TVA 8,5%) | Frais de transport, pour les livraisons hors France Métropolitaine (TVA 20%)</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr"/>
@@ -4362,12 +4350,12 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>El314</t>
+          <t>El224d</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Si oui, préciser</t>
+          <t>Si oui préciser si elles concernent l'assurance livraison</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
@@ -4378,18 +4366,18 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Sur devis | Inclus dans les prix | Non concerné pour la direction/univers | Non concerné pour l'offre
-Texte : Sur devis | Inclus dans les prix</t>
+          <t>Liste proposée : Oui | Assurance pour les livraisons hors France Métropolitaine (TVA 0%) | Non | Absence d'assurance pour la livraison
+Texte : Oui, Assurance pour les livraisons hors France Métropolitaine (TVA 0%) | Non, Absence d'assurance pour la livraison</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr"/>
@@ -4411,12 +4399,12 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>El316a</t>
+          <t>El258c</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Préciser le périmètre concerné par l'actualisation des prix fermes</t>
+          <t>L'offre inclut-elle des exigences en matière d'impact environnemental du transport?</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
@@ -4427,18 +4415,18 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui | les modalités de variation des prix sont identiques pour tous les lots | Non | les modalités de variation des prix sont différentes en fonction des lots
-Texte : des matériels | des prestations annexes | des prestations de maintenance | des modulations de garantie</t>
+          <t>Liste proposée : Oui, l'offre inclut des exigences en matière d'impact environnemental du transport | Non, l'offre n'inclut pas d'exigences en matière d'impact environnemental du transport
+Texte : Oui, l'offre inclut des exigences en matière d'impact environnemental du transport | Oui, l'offre n'inclut pas d'exigences en matière d'impact environnemental du transport</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr"/>
@@ -4460,12 +4448,12 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>El321</t>
+          <t>El260a</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Si oui, laquelle est la première révision des prix</t>
+          <t>Les produits issus du réemploi/réutilisation sont-ils intégrés dans l'offre (exemple : architecture lot dédié, facultatif libre ...)?</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
@@ -4476,18 +4464,18 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Par seuil de déclenchement | Sur indices | Sur tarif public
-Texte : Première révision classique | Par seuil de déclenchement | Sur indices | Sur tarif public</t>
+          <t>Liste proposée : Oui, l'offre/les lots intègre(nt) des produits issus du réemploi/réutilisation | Non, l'offre n'intègre pas des produits issus du réemploi/réutilisation
+Texte : Oui, l'offre intègre des produits issus du réemploi/réutilisation | Non, l'offre n'intègre pas des produits issus du réemploi/réutilisation</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr"/>
@@ -4509,12 +4497,12 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>El328</t>
+          <t>El260b</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Si oui, préciser la période de calcul (X mois / X périodes successives / Autre)</t>
+          <t>Une obligation imposant aux fournisseurs de remettre pendant l'exécution du marché l'information sur l'intégration de matière recyclée dans les produits est-elle bien intégrée pour les lots le nécessitant (produits textiles, consommables d'impression, papier, engins de transports...)?</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -4525,18 +4513,18 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : 12 mois | Autre
-Texte : X mois / X périodes successives / Autre</t>
+          <t>Liste proposée : Oui, l'offre/les lots prévoi(en)t pour le titulaire l'obligation de remettre pendant l'exécution du marché ces informations | Non, l'offre ne prévoit pas la remise de ces informations
+Texte : Oui, l'offre prévoit pour le titulaire l'obligation de remettre pendant l'exécution du marché ces informations | Non, l'offre ne prévoit pas la remise de ces informations</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr"/>
@@ -4558,12 +4546,12 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>El335f</t>
+          <t>El260g</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Si non, cette obligation fait-elle l'objet d'un critère d'analyse des offres ?</t>
+          <t>Les lots prévoient-ils une traçabilité sociale des chaines d'approvisionnement ?</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
@@ -4574,18 +4562,18 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui, cette obligation fait l'objet d'un critère d'analyse des offres | Oui, cette obligation fait l'objet d'un critère d'analyse des offres;Non, absence de critère d'analyse des offres
-Texte : Oui, cette obligation fait l'objet d'un critère d'analyse des offres | Non, absence de critère d'analyse des offres</t>
+          <t>Liste proposée : Oui, traçabilité sociale des chaines d'approvisionnement pour tous les lots des univers concernés | Non, pas de traçabilité sociale des chaines d'approvisionnement pour tous les lots des univers concernés
+Texte : Oui, traçabilité sociale des chaines d'approvisionnement pour tous les lots des univers concernés | Non, pas de traçabilité sociale des chaines d'approvisionnement pour tous les lots des univers concernés.</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr"/>
@@ -4607,12 +4595,12 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>El339c</t>
+          <t>El268</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>La possibilité de réalisation d'un audit lors de l'exécution du marché est-il prévu à l'offre?</t>
+          <t>Si oui, à compter de quel délai le titulaire s'engage à communiquer au bénéficiaire le droit d'utilisation des logiciels concédés ?  (si délai autre que le choix sur liste, saisir directement le délai dans la réponse)</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
@@ -4623,18 +4611,18 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui, un audit est prévu dans le cadre de l'exécution du marché | Non absence d'audit prévu au marché
-Texte : Oui, un audit est prévu au démarrage des prestations | Non, absence d'audit prévu au démarrage des prestations</t>
+          <t>Liste proposée : Dans un délai de 30 jours | Dans un délai de 7 jours
+Texte : Champ libre</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr"/>
@@ -4656,12 +4644,12 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>El352</t>
+          <t>El270</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Modalités de sélection</t>
+          <t>L'offre antérieure affiche-t'elle un stock fournisseur  ?</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
@@ -4672,18 +4660,18 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Pas de niveau minimal imposé | Chiffres d’affaires minimum en montant | Ratio financier inférieur ou égal à XX% - CA global du candidat | Ratio financier inférieur ou égal à XX% - CA objet du (des) lot(s) du candidat
-Texte : Pas de niveau minimal imposé | Chiffres d’affaires minimum en montant | Ratio financier inférieur ou égal à un pourcentage du CA global du candidat | Ratio financier inférieur ou égal à un pourcentage du CA objet du (des) lot(s) du candidat</t>
+          <t>Liste proposée : Oui | l'offre antérieure affiche un stock fournisseur | Non | l'offre antérieure n'affiche pas de stock fournisseur
+Texte : Oui, l'offre antérieure affiche un stock fournisseur | Non, l'offre antérieure n'affiche pas de stock fournisseur</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr"/>
@@ -4705,34 +4693,34 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>El359</t>
+          <t>El271</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Si oui, le versement d'une prime est-elle envisagée ?</t>
+          <t>Si oui, préciser à la charge de qui</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+          <t>La liste nommée ListeEl271 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui | Non
-Texte : Oui / Non</t>
+          <t>Liste proposée : Client | Fournisseur | UGAP
+Texte : Client | Fournisseur (Web service) | UGAP</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr"/>
@@ -4754,34 +4742,34 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>El488</t>
+          <t>El30</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Si oui, préciser si les durées sont conformes au standard (≤ 2 ans pour les produits neufs et ≤ 1 an pour les produits reconditionnés)</t>
+          <t>Si autres, préciser si les bénéficiaires concernés sont les Sociétés d’autoroutes pou les Délégataires de service public</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+          <t>La liste nommée ListeEl30 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : oui | durée standard applicable | non | durée spécifique applicable
-Texte : oui, durée standard applicable | non, durée spécifique applicable</t>
+          <t>Liste proposée : Sociétés d’autoroutes | Délégataires de service public | Caisses | Entreprises | Autre
+Texte : Sociétés d’autoroutes | Délégataires de service public | Caisses et entreprises | Autre</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr"/>
@@ -4803,12 +4791,12 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>El494</t>
+          <t>El302</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Si mono échéance, préciser la périodicité applicable</t>
+          <t>Le principe d'engagement maximum sans minimum s'applique-t 'il ?</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
@@ -4819,18 +4807,18 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Paiement unique | mensuelle | trimestrielle | Semestrielle | annuelle
-Texte : Mensuelle | trimestrielle | semestrielle, annuelle</t>
+          <t>Liste proposée : Oui, le principe d'engagement maximum sans minimum s'applique | Non, dérogation au standard
+Texte : Oui, le principe d'engagement maximum avec montants estimés s'applique | Non, dérogation au standard</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr"/>
@@ -4852,34 +4840,34 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>El494b</t>
+          <t>El308</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Si multi échéance, préciser la périodicité applicable</t>
+          <t>Préciser les modalités particulières de prix applicables</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+          <t>La liste nommée ListeEl308 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Paiement unique | mensuelle | trimestrielle | Semestrielle | annuelle
-Texte : Mensuelle | trimestrielle | semestrielle, annuelle</t>
+          <t>Liste proposée : Référence forfaitaire petite commande | Minima de commande | Politique de remise (ex remise sur tarif public) | Barème dégressif en fonction des quantités | Application d'un taux d'intermédiationsur prix d'achat | Conditions de livraison | Surcoût (îles littorales)
+Texte : Référence forfaitaire petite commande | Minima de commande | Politique de remise (ex remise sur tarif public) | Barème dégressif en fonction des quantités | Conditions de livraison | surcoût (îles littorales)</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr"/>
@@ -4901,12 +4889,12 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>El506a</t>
+          <t>El30b</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Préciser le périmètre concerné par la révision sur tarif public à tout moment</t>
+          <t>l'UGAP est-elle bénéficiaire ?</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
@@ -4917,18 +4905,18 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui | les modalités de variation des prix sont identiques pour tous les lots | Non | les modalités de variation des prix sont différentes en fonction des lots
-Texte : des matériels | des prestations annexes | des prestations de maintenance | des modulations de garantie</t>
+          <t>Liste proposée : Oui, l'UGAP est bénéficaire de l'offre | Non, l'UGAP n'est pas bénéficiaire de l'offre
+Texte : Oui, l'UGAP est bénéficiaire de l'offre | Non, l'UGAP n'est pas bénéficiaire de l'offre</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr"/>
@@ -4950,12 +4938,12 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>El510a</t>
+          <t>El314</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Préciser le périmètre concerné par la révision sur tarif public à date fixe ou anniversaire</t>
+          <t>Si oui, préciser</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
@@ -4966,18 +4954,18 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui | les modalités de variation des prix sont identiques pour tous les lots | Non | les modalités de variation des prix sont différentes en fonction des lots
-Texte : des matériels | des prestations annexes | des prestations de maintenance | des modulations de garantie</t>
+          <t>Liste proposée : Sur devis | Inclus dans les prix | Non concerné pour la direction/univers | Non concerné pour l'offre
+Texte : Sur devis | Inclus dans les prix</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K87" s="3" t="inlineStr"/>
@@ -4999,34 +4987,34 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>El511</t>
+          <t>El316</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Le montant total estimé de la procédure est-il supérieur à 250 millions d'euros HT ?</t>
+          <t>Quelles sont les modalités de variation des prix   ?</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+          <t>La liste nommée ListeEl316 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui | Non
-Texte : Oui, le principe d'engagement maximum avec montants estimés s'applique | Non, dérogation au standard</t>
+          <t>Liste proposée : Prix fermes | Prix révisables sur tarif public à tout moment | Prix révisables sur tarif public à date fixe ou anniversaire | Prix révisables sur indice | Taux de remise sur tarif public | Autre
+Texte : Prix fermes | Prix révisables sur tarif public à la date d'anniversaire | Prix révisables sur tarif public à tout moment | Prix révisables sur tarif public à date fixe | Prix révisables sur indice | Taux de remise sur tarif public | Autre</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr"/>
@@ -5048,12 +5036,12 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>El5c</t>
+          <t>El316a</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Quel est le(s) format(s) d'émission de commande d’achat envisagé(s) pour les prestations de location/maintenance ?</t>
+          <t>Préciser le périmètre concerné par l'actualisation des prix fermes</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
@@ -5064,18 +5052,18 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Mono échéance | Multi échéance | Mono échéance &amp; Multi échéance
-Texte : Mono échéance | Multi échéance | Mixte (Mono et Multi échéance)</t>
+          <t>Liste proposée : Oui | les modalités de variation des prix sont identiques pour tous les lots | Non | les modalités de variation des prix sont différentes en fonction des lots
+Texte : des matériels | des prestations annexes | des prestations de maintenance | des modulations de garantie</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr"/>
@@ -5097,12 +5085,12 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>El5e</t>
+          <t>El321</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Quelle est la périodicité de commande d’achat envisagée en Multi échéance ?</t>
+          <t>Si oui, laquelle est la première révision des prix</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
@@ -5113,18 +5101,18 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Unique | Mensuelle | Trimestrielle | Annuelle | Autre | Non concerné pour l'offre
-Texte : Unique | Mensuelle | Trimestrielle | Annuelle | Autre</t>
+          <t>Liste proposée : Par seuil de déclenchement | Sur indices | Sur tarif public
+Texte : Première révision classique | Par seuil de déclenchement | Sur indices | Sur tarif public</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr"/>
@@ -5146,34 +5134,34 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>El69</t>
+          <t>El327</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Le mode de passation de l'appel d'offres est-il ouvert ?</t>
+          <t>Si oui, quelle est la base de calcul de la clause de sauvegarde</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+          <t>La liste nommée ListeEl327 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui, mode de passation en Appel d'Offres Ouverts | Non, autre mode de passation
-Texte : Oui, mode de passation en Appel d'Offres Ouvert | Non, autre mode de passation</t>
+          <t>Liste proposée : Prix initial | Dernier prix révisé | Indice inital | Dernier indice révisé | Non concerné pour l'offre
+Texte : Prix initial | Dernier prix révisé | indice inital | dernier indice révisé</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K91" s="3" t="inlineStr"/>
@@ -5195,12 +5183,12 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>El70</t>
+          <t>El328</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Si non, préciser le mode de passation et justifier du choix</t>
+          <t>Si oui, préciser la période de calcul (X mois / X périodes successives / Autre)</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
@@ -5211,18 +5199,18 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Appel d'offres restreint | Dialogue compétitif | Procédure concurrentielle avec négociation | SAD avec enchères | SAD sans enchères | Non concerné pour l'offre
-Texte : Appel d'offres restreint / Dialogue compétitif / Procédure concurrentielle avec négociation / SAD avec enchères / SAD sans enchères</t>
+          <t>Liste proposée : 12 mois | Autre
+Texte : X mois / X périodes successives / Autre</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr"/>
@@ -5244,34 +5232,34 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>El71</t>
+          <t>El332</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Type d’accords-cadres</t>
+          <t>Une période de neutralisation des prestations (hors SAV) est-elle à prévoir ?</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+          <t>La liste nommée ListeEl332 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : AC-Bons de commande | AC-Bons de commande | AC-Marchés subséquents et Bons de commande
-Texte : AC-Marchés subséquents | AC-Bons de commande | AC-Marchés subséquents et Bons de commande</t>
+          <t>Liste proposée : Oui, Période de congés | Oui, Changement de modèle | Oui, Impact industriel lourd | Oui, En Chine pendant Golden Week et Nouvel An Chinois | Oui, Autre | Non, aucune période de neutralisation
+Texte : Non, aucune période de neutralisation | Période de congés | Changement de modèle | impact industriel lourd | Autre</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K93" s="3" t="inlineStr"/>
@@ -5293,34 +5281,34 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>El77</t>
+          <t>El334</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Quelles sont les modalités d’intervention de l’UGAP ?</t>
+          <t>Si autre, préciser (en cas de cas non listé, préciser directement les information en texte libre)</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+          <t>La liste nommée ListeEl334 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Offre exécutée | Offre non exécutée | Offre exécutée &amp; Offre non exécutée
-Texte : Offre exécutée | Offre non exécutée | Mixte</t>
+          <t>Liste proposée : Exécution de prestations annexes (CCAP, Annexe 1 à l’acte d’engagement) | Accompagnement au déploiement auprès des bénéficiaires de l’UGAP (CCAP, Questionnaire Qualité de service) | Documentation/obligation liée au MDR et CE IVD-R
+Texte : Alimentation et ou validation du référencement | Documentation SAV | Outils | Impératifs logistiques UGAP (tracabilité…) | Eléments pour publication (ex : photo) | Aides à la commercialisation (prêt de matériel...) | Autre</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr"/>
@@ -5342,12 +5330,12 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>El78l</t>
+          <t>El335f</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Quelles est la règle d'attribution des bons de commande  ?</t>
+          <t>Si non, cette obligation fait-elle l'objet d'un critère d'analyse des offres ?</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
@@ -5358,18 +5346,18 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : A la survenance du besoin | par périodicité
-Texte : A la survenance du besoin | Périodicité</t>
+          <t>Liste proposée : Oui, cette obligation fait l'objet d'un critère d'analyse des offres | Oui, cette obligation fait l'objet d'un critère d'analyse des offres;Non, absence de critère d'analyse des offres
+Texte : Oui, cette obligation fait l'objet d'un critère d'analyse des offres | Non, absence de critère d'analyse des offres</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K95" s="3" t="inlineStr"/>
@@ -5391,12 +5379,12 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>El81b</t>
+          <t>El339c</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Si non, préciser la durée du marché toutes reconductions comprises (si durée autre que le choix sur liste, saisir directement le délai dans la réponse)</t>
+          <t>La possibilité de réalisation d'un audit lors de l'exécution du marché est-il prévu à l'offre?</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
@@ -5407,19 +5395,18 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : 1.Période initiale de 48 mois ferme pour l’ensemble des produits et prestations objets du marché
-2.2nde période de 96 mois ferme restreinte aux commandes rattachées à une commande initiale sur le périmètre limitatif
-Texte : Nombre de mois</t>
+          <t>Liste proposée : Oui, un audit est prévu dans le cadre de l'exécution du marché | Non absence d'audit prévu au marché
+Texte : Oui, un audit est prévu au démarrage des prestations | Non, absence d'audit prévu au démarrage des prestations</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr"/>
@@ -5441,34 +5428,37 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>El82</t>
+          <t>El343</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Des travaux d'interfacage ou de déploiement long sont-ils prévus nécessitant des échanges avec le titulaire avant ouverture du marché à la commercialisation ?</t>
+          <t>Si oui, préciser si un traitement particulier doit être mis en place sur les iles littorales (mise en œuvre de la garantie contractuelle, prestations associées de base, recette technique le cas échéant, prestations associées optionnelles, autres...</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+          <t>La liste nommée ListeEl343 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Liste déroulante : Oui, un déploiement long est prévu | Oui, des travaux d'interfaçage et de déploiement long sont prévus | Non, absence de travaux d'interfacage ou de déploiement long
-Texte : Oui, travaux d'interfacage sont prévus | Oui, un déploiement long est prévu | Oui, des travaux d'interfaçage et de déploiement long sont prévus | Non, absence de travaux d'interfacage ou de déploiement long</t>
+          <t>Liste proposée : Les îles littorales : Garantie contractuelle | Les îles littorales : Prestations incluses dans le prix du matériel de base | Les îles littorales : Prestations annexes non incluses dans le prix du matériel de base.
+Texte : Les îles littorales :
+o	Garantie contractuelle,
+o	Prestations incluses dans le prix du matériel de base,
+o	Prestations annexes non incluses dans le prix du matériel de base.</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>L'outil propose la liste déroulante (celle que les acheteurs utilisaient).</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>Confirmer la liste déroulante, ou indiquer la bonne liste</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K97" s="3" t="inlineStr"/>
@@ -5480,47 +5470,44 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Structure</t>
+          <t>Liste de choix</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>À trancher</t>
+          <t>À vérifier</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>THM_ElT445</t>
+          <t>El35</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Généralités</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>05.0 GARANTIE _SAV_MAINTENANCE</t>
-        </is>
-      </c>
+          <t>Supports utilisés</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Questions placées directement sous le chapitre, sans thème.</t>
+          <t>La liste nommée ListeEl35 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Questions : El445</t>
+          <t>Liste proposée : Print (catalogue général, catalogue spécialisé, plaquettes fournisseurs…) | Web (ugap.fr) | Animation (emailing, communiqué de presse, push…) | Non concerné pour l'offre
+Texte : Print (catalogue général, catalogue spécialisé, plaquettes fournisseurs…) | Web (ugap.fr) | Animation (emailing, communiqué de presse, push…)</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Un thème « Généralités » a été créé pour les afficher.</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>Valider le nom du thème, ou indiquer le thème à créer</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr"/>
@@ -5532,47 +5519,44 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Structure</t>
+          <t>Liste de choix</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>À trancher</t>
+          <t>À vérifier</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>THM_ElT453</t>
+          <t>El351</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>CONFORMITE - Protection des données personnelles</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>08.0  CONFORMITE - Protection des données personnelles</t>
-        </is>
-      </c>
+          <t>Eléments pris en compte pour l'analyse du critère capacité professionnelles et techniques</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Questions placées directement sous le chapitre, sans thème.</t>
+          <t>La liste nommée ListeEl351 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Questions : El263, El264, El490, El265</t>
+          <t>Liste proposée : Références : liste des principales fournitures ou services effectuées au cours des 3 dernières années (attention un candidat ne peut pas être éliminé pour ce seul motif) | Titres d’études et professionnels de l’opérateur économique et/ou des cadres de l’entreprise, et notamment des responsables de prestations de services de même nature que celle du marché | Certificats de qualifications professionnelles ou équivalents établis par des organismes indépendants | Certificats de qualité ou équivalent | Indication des systèmes de gestion et de suivi de la chaine d’approvisionnement que le candidat pourra mettre en œuvre | Outillage, matériel et équipement technique dont le candidat dispose pour la réalisation du marché (impossible de demander sur 3 ans) | Effectifs moyens annuels et importance du personnel d’encadrement, pour chacune des 3 dernières années
+Texte : liste des principales fournitures ou services effectuées au cours des 3 dernières années | Titres d’études et professionnels de l’opérateur économique et/ou des cadres de l’entreprise, et notamment des responsables de prestations de services de même nature que celle du marché | Certificats de qualifications professionnelles ou équivalents établis par des organismes indépendants, Certificats de qualité ou équivalent | Indication des systèmes de gestion et de suivi de la chaine d’approvisionnement que le candidat pourra mettre en œuvre | Outillage, matériel et équipement technique dont le candidat dispose pour la réalisation du marché | Effectifs moyens annuels et importance du personnel d’encadrement, pour chacune des 3 dernières années.</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Un thème « CONFORMITE - Protection des données personnelles » a été créé pour les afficher.</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>Valider le nom du thème, ou indiquer le thème à créer</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K99" s="3" t="inlineStr"/>
@@ -5584,47 +5568,44 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Structure</t>
+          <t>Liste de choix</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>À trancher</t>
+          <t>À vérifier</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>THM_ElT491</t>
+          <t>El352</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>DROITS DE PROPRIETE INTELECTUELLE</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>09.0 DROITS DE PROPRIETE INTELECTUELLE</t>
-        </is>
-      </c>
+          <t>Modalités de sélection</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Questions placées directement sous le chapitre, sans thème.</t>
+          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Questions : El266, El268</t>
+          <t>Liste proposée : Pas de niveau minimal imposé | Chiffres d’affaires minimum en montant | Ratio financier inférieur ou égal à XX% - CA global du candidat | Ratio financier inférieur ou égal à XX% - CA objet du (des) lot(s) du candidat
+Texte : Pas de niveau minimal imposé | Chiffres d’affaires minimum en montant | Ratio financier inférieur ou égal à un pourcentage du CA global du candidat | Ratio financier inférieur ou égal à un pourcentage du CA objet du (des) lot(s) du candidat</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Un thème « DROITS DE PROPRIETE INTELECTUELLE » a été créé pour les afficher.</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>Valider le nom du thème, ou indiquer le thème à créer</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr"/>
@@ -5636,48 +5617,1430 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Standards</t>
+          <t>Liste de choix</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>À trancher</t>
+          <t>À vérifier</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>DAG_Energie_et_environnement</t>
+          <t>El359</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Standard de direction</t>
+          <t>Si oui, le versement d'une prime est-elle envisagée ?</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Le standard de direction « DAG_Energie_et_environnement » est proposé en page de garde, mais n'a aucune colonne dans 140-Standards.</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr"/>
+          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : Oui | Non
+Texte : Oui / Non</t>
+        </is>
+      </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Toutes les questions sont « spécifiques à l'offre » (Sp) pour cette direction : aucun standard, aucune réponse pré-remplie.</t>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>Créer les standards de cette direction, ou retirer ce choix de la page de garde</t>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
         </is>
       </c>
       <c r="K101" s="3" t="inlineStr"/>
       <c r="L101" s="3" t="inlineStr"/>
     </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>El361</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Le titulaire s'engage a fournir :</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>La liste nommée ListeEl361 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : Fiches technico-commerciales | Images numériques | Publipostages | Nuanciers | Banque de donnée de type AUTOCAD | Matériel de démonstration | Guide de vente | Non concerné pour l'offre
+Texte : Fiches technico-commerciales | images numériques | Publipostages | Nuanciers | Une banque de donnée de type AUTOCAD | Matériel de démonstration | Guide de vente</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr"/>
+      <c r="L102" s="3" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>El370</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Quelles sont les modalités de maintenance (préventive, corrective…) prévues ?</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>La liste nommée ListeEl370 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : Maintenance préventive | Maintenance corrective/curative | Non concerné pour l'offre
+Texte : préventive | corrective/curative</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr"/>
+      <c r="L103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>El377</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Si maintenance corrective/curative, l'intervention du titulaire vise quelle remise en état ?</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>La liste nommée ListeEl377 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : Remise en état des Matériels | Remise en état des Installations et logiciels | Non concerné pour l'offre
+Texte : remise en état des Matériels | remise en état des Installations et logiciels</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr"/>
+      <c r="L104" s="3" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>El488</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Si oui, préciser si les durées sont conformes au standard (≤ 2 ans pour les produits neufs et ≤ 1 an pour les produits reconditionnés)</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : oui | durée standard applicable | non | durée spécifique applicable
+Texte : oui, durée standard applicable | non, durée spécifique applicable</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr"/>
+      <c r="L105" s="3" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>El493</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Si oui, préciser la périodicité applicable</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>La liste nommée ListeEl493 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : Paiement unique | Mensuelle | Trimestrielle | Semestrielle | Annuelle
+Texte : Mensuelle | trimestrielle | semestrielle, annuelle</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr"/>
+      <c r="L106" s="3" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>El494</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Si mono échéance, préciser la périodicité applicable</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : Paiement unique | mensuelle | trimestrielle | Semestrielle | annuelle
+Texte : Mensuelle | trimestrielle | semestrielle, annuelle</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr"/>
+      <c r="L107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>El494b</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Si multi échéance, préciser la périodicité applicable</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : Paiement unique | mensuelle | trimestrielle | Semestrielle | annuelle
+Texte : Mensuelle | trimestrielle | semestrielle, annuelle</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr"/>
+      <c r="L108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>El500c</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Si couverture géographique obligatoire à l'étranger, l'étranger comprend</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>La liste nommée ListeEl500c (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : Représentations françaises dans l’Union Européenne | Représentations françaises à l’étranger | Monaco, Suisse, Andorre | Pays de l'Espace Economique Européen (EEE) | Autres
+Texte : Représentations françaises dans l’Union Européenne | Représentations françaises à l’étranger | Monaco, Suisse, Andorre | EEE | Autres</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr"/>
+      <c r="L109" s="3" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>El506a</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Préciser le périmètre concerné par la révision sur tarif public à tout moment</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : Oui | les modalités de variation des prix sont identiques pour tous les lots | Non | les modalités de variation des prix sont différentes en fonction des lots
+Texte : des matériels | des prestations annexes | des prestations de maintenance | des modulations de garantie</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr"/>
+      <c r="L110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>El510a</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Préciser le périmètre concerné par la révision sur tarif public à date fixe ou anniversaire</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : Oui | les modalités de variation des prix sont identiques pour tous les lots | Non | les modalités de variation des prix sont différentes en fonction des lots
+Texte : des matériels | des prestations annexes | des prestations de maintenance | des modulations de garantie</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr"/>
+      <c r="L111" s="3" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>El511</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Le montant total estimé de la procédure est-il supérieur à 250 millions d'euros HT ?</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : Oui | Non
+Texte : Oui, le principe d'engagement maximum avec montants estimés s'applique | Non, dérogation au standard</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr"/>
+      <c r="L112" s="3" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>El59</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Préciser la couverture géographique à caractère obligatoire des matériels et/ou prestations à livrer ou exécuter par le titulaire  Note:  DROM = Guadeloupe, Martinique, Guyane, Réunion et Mayotte COM pour besoins non soumis à une disposition de droit local = St Pierre &amp; Miquelon, St Barthélemy, St …</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>La liste nommée ListeEl59 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : France métropolitaine | France continentale | Corse et îles littorales non desservies par un pont gratuit | DROM | COM inclus TAAF | COM hors TAAF | Etranger | Autres
+Texte : France métropolitaine | France continentale | Corse et îles littorales non desservies par un pont gratuit | DROM | COM | Etranger</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr"/>
+      <c r="L113" s="3" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>El5c</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Quel est le(s) format(s) d'émission de commande d’achat envisagé(s) pour les prestations de location/maintenance ?</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : Mono échéance | Multi échéance | Mono échéance &amp; Multi échéance
+Texte : Mono échéance | Multi échéance | Mixte (Mono et Multi échéance)</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr"/>
+      <c r="L114" s="3" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>El5e</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Quelle est la périodicité de commande d’achat envisagée en Multi échéance ?</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : Unique | Mensuelle | Trimestrielle | Annuelle | Autre | Non concerné pour l'offre
+Texte : Unique | Mensuelle | Trimestrielle | Annuelle | Autre</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr"/>
+      <c r="L115" s="3" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>El60b</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Si oui, préciser la couverture géographique à caractère facultatif des matériels et/ou prestations à livrer ou exécuter par le titulaire  Note:  DROM = Guadeloupe, Martinique, Guyane, Réunion et Mayotte COM pour besoins non soumis à une disposition de droit local = St Pierre &amp; Miquelon, St Barthéle…</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>La liste nommée ListeEl60b (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : France métropolitaine | France continentale | Corse et îles littorales non desservies par un pont gratuit | DROM | COM inclus TAAF | COM hors TAAF | Etranger | Autres
+Texte : France métropolitaine | France continentale | Corse et îles littorales non desservies par un pont gratuit | DROM | COM | Etranger</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr"/>
+      <c r="L116" s="3" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>El60c</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Si couverture géographique facultative à l'étranger, l'étranger comprend</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>La liste nommée ListeEl60c (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : Représentations françaises dans l’Union Européenne | Représentations françaises à l’étranger | Monaco, Suisse, Andorre | Pays de l'Espace Economique Européen (EEE) | Autres
+Texte : Représentations françaises dans l’Union Européenne | Représentations françaises à l’étranger | Monaco, Suisse, Andorre | EEE | Autres</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr"/>
+      <c r="L117" s="3" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>El69</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Le mode de passation de l'appel d'offres est-il ouvert ?</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : Oui, mode de passation en Appel d'Offres Ouverts | Non, autre mode de passation
+Texte : Oui, mode de passation en Appel d'Offres Ouvert | Non, autre mode de passation</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr"/>
+      <c r="L118" s="3" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>El70</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Si non, préciser le mode de passation et justifier du choix</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : Appel d'offres restreint | Dialogue compétitif | Procédure concurrentielle avec négociation | SAD avec enchères | SAD sans enchères | Non concerné pour l'offre
+Texte : Appel d'offres restreint / Dialogue compétitif / Procédure concurrentielle avec négociation / SAD avec enchères / SAD sans enchères</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr"/>
+      <c r="L119" s="3" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>El71</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Type d’accords-cadres</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : AC-Bons de commande | AC-Bons de commande | AC-Marchés subséquents et Bons de commande
+Texte : AC-Marchés subséquents | AC-Bons de commande | AC-Marchés subséquents et Bons de commande</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr"/>
+      <c r="L120" s="3" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>El73</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Si AC BDC multi attribué ou mixte (Mono et multi attribué) préciser la modalité de multi attribution</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>La liste nommée ListeEl73 (fenêtre de choix multiples) ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : Sur règle d’attribution définie au CCAP sur la base d’un questionnaire client ou d’une attestation de choix dérogatoire sans règle d’attribution à la défaillance, | Sur règle d’attribution définie au CCAP sur la base d’un questionnaire client ou d’une attestation de choix dérogatoire et d’une règle d’attribution à la défaillance | Sur règle d’attribution définie au CCAP sur la base de quantité minimale d’engagement au marché sans défaillance, | Sur règle d’attribution standard à la survenance du besoin et règle d’attribution à la défaillance | Sur règle d’attribution standard à la survenance du besoin sans règle d’attribution à la défaillance | Sur règle d'attribution à la défaillance temporaire et/ou définitive
+Texte : Sur règle d’attribution définie au CCAP sur la base d’un questionnaire client ou d’une attestation de choix dérogatoire sans règle d’attribution à la défaillance, | Sur règle d’attribution définie au CCAP sur la base d’un questionnaire client ou d’une attestation de choix dérogatoire et d’une règle d’attribution à la défaillance | Sur règle d’attribution définie au CCAP sur la base de quantité minimale d’engagement au marché sans défaillance, | Sur règle d’attribution standard à la survenance du besoin et règle d’attribution à la défaillance | Sur règle d’attribution standard à la survenance du besoin sans règle d’attribution à la défaillance | Sur règle d'attribution à la défaillance temporaire et/ou définitive | Autres</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr"/>
+      <c r="L121" s="3" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>El77</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Quelles sont les modalités d’intervention de l’UGAP ?</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : Offre exécutée | Offre non exécutée | Offre exécutée &amp; Offre non exécutée
+Texte : Offre exécutée | Offre non exécutée | Mixte</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr"/>
+      <c r="L122" s="3" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>El78l</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Quelles est la règle d'attribution des bons de commande  ?</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : A la survenance du besoin | par périodicité
+Texte : A la survenance du besoin | Périodicité</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr"/>
+      <c r="L123" s="3" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>El81b</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Si non, préciser la durée du marché toutes reconductions comprises (si durée autre que le choix sur liste, saisir directement le délai dans la réponse)</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : 1.Période initiale de 48 mois ferme pour l’ensemble des produits et prestations objets du marché
+2.2nde période de 96 mois ferme restreinte aux commandes rattachées à une commande initiale sur le périmètre limitatif
+Texte : Nombre de mois</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr"/>
+      <c r="L124" s="3" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Liste de choix</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>El82</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Des travaux d'interfacage ou de déploiement long sont-ils prévus nécessitant des échanges avec le titulaire avant ouverture du marché à la commercialisation ?</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>La liste déroulante de la cellule ne correspond pas au texte de la colonne « Choix de réponse ».</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>Liste proposée : Oui, un déploiement long est prévu | Oui, des travaux d'interfaçage et de déploiement long sont prévus | Non, absence de travaux d'interfacage ou de déploiement long
+Texte : Oui, travaux d'interfacage sont prévus | Oui, un déploiement long est prévu | Oui, des travaux d'interfaçage et de déploiement long sont prévus | Non, absence de travaux d'interfacage ou de déploiement long</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>L'outil propose la liste que voyaient les acheteurs dans l'outil d'origine.</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>Confirmer cette liste, ou indiquer la bonne liste</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr"/>
+      <c r="L125" s="3" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>À trancher</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>THM_ElT445</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Généralités</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>05.0 GARANTIE _SAV_MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Questions placées directement sous le chapitre, sans thème.</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Questions : El445</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>Un thème « Généralités » a été créé pour les afficher.</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>Valider le nom du thème, ou indiquer le thème à créer</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr"/>
+      <c r="L126" s="3" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>À trancher</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>THM_ElT453</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>CONFORMITE - Protection des données personnelles</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>08.0  CONFORMITE - Protection des données personnelles</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Questions placées directement sous le chapitre, sans thème.</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>Questions : El263, El264, El490, El265</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>Un thème « CONFORMITE - Protection des données personnelles » a été créé pour les afficher.</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>Valider le nom du thème, ou indiquer le thème à créer</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr"/>
+      <c r="L127" s="3" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>À trancher</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>THM_ElT491</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>DROITS DE PROPRIETE INTELECTUELLE</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>09.0 DROITS DE PROPRIETE INTELECTUELLE</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Questions placées directement sous le chapitre, sans thème.</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>Questions : El266, El268</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>Un thème « DROITS DE PROPRIETE INTELECTUELLE » a été créé pour les afficher.</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>Valider le nom du thème, ou indiquer le thème à créer</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="inlineStr"/>
+      <c r="L128" s="3" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Standards</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>À trancher</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>DAG_Energie_et_environnement</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Standard de direction</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr"/>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Le standard de direction « DAG_Energie_et_environnement » est proposé en page de garde, mais n'a aucune colonne dans 140-Standards.</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr"/>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>Toutes les questions sont « spécifiques à l'offre » (Sp) pour cette direction : aucun standard, aucune réponse pré-remplie.</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>Créer les standards de cette direction, ou retirer ce choix de la page de garde</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr"/>
+      <c r="L129" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L101"/>
+  <autoFilter ref="A1:L129"/>
   <dataValidations count="1">
-    <dataValidation sqref="K2:K101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Accepter la proposition,Autre correction (préciser),Ne rien changer"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5691,7 +7054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C268"/>
+  <dimension ref="A1:C210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -5719,1275 +7082,1275 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Choix repris du texte « Choix de réponse » (ni liste déroulante, ni liste nommée)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>El0a</t>
+          <t>El325</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Ensemble batterie | Location de batterie | Acquisition de batterie | Piles à combustibles (hydrogène) | Acquisition de véhicules | Acquisition de véhicules à hydrogène | Acquisition de véhicules 100%…</t>
+          <t>Liste de choix ou texte : Oui, application d'une clause de sauvegarde | Non, absence de clause de sauvegarde</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Identifiant écrit différemment (majuscules)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>El103</t>
+          <t>EL492</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Absence d'application de marge sur les taxes d'immatriculation | Surcoût Drom Com | Indeminité et annulation et modification de commande | Reprise de matériel</t>
+          <t>EL492 dans 3-Elaboration.O, El492 dans 140-Standards</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Identifiant écrit différemment (majuscules)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>El104</t>
+          <t>El260b</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Clause promo | Clause devis 5% | Clause de réexamen | Avenant | marchés de prestations similaires</t>
+          <t>El260b dans 3-Elaboration.O, el260b dans 140-Standards</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Identifiant écrit différemment (majuscules)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>El104b</t>
+          <t>El260c</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Pour évolutions techniques ou technologiques | Suite à évolutions techniques et règlementaires | Ajouts nécessaires à bonne exécution de marché | En cas de circonstances imprévisibles | Modifications…</t>
+          <t>El260c dans 3-Elaboration.O, el260c dans 140-Standards</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Identifiant écrit différemment (majuscules)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>El107</t>
+          <t>El260c</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Diminution du prix net d'un ou de plusieurs matériel(s)/prestations | La mise en place de conditionnements promotionnels (vente de lots) | La mise en place de packages dit promotionnels regroupant pl…</t>
+          <t>el260c dans 100-Parametres</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Identifiant écrit différemment (majuscules)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>El111</t>
+          <t>El260c</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Qualification du besoin par le titulaire et rédaction d’un dossier technique le cas échéant | fiche de vente | prévisite du titulaire | questionnaire client (offre plurielle) | fiche de recensement |…</t>
+          <t>el260c dans 100-Parametres</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Identifiant écrit différemment (majuscules)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>El114</t>
+          <t>El260d</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Devis tripartite / CCM / E-commerce / réel constaté /Autre</t>
+          <t>El260d dans 3-Elaboration.O, el260d dans 140-Standards</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Identifiant écrit différemment (majuscules)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>El123</t>
+          <t>El260d</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Devis tripartite | CCM | E-commerce | réel constaté | Autre</t>
+          <t>el260d dans 100-Parametres</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Identifiant écrit différemment (majuscules)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>El132b</t>
+          <t>El260e</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : mensuelle,trimestrielle,semestrielle | annuelle</t>
+          <t>El260e dans 3-Elaboration.O, el260e dans 140-Standards</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Identifiant écrit différemment (majuscules)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>El134</t>
+          <t>El260e</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Location maintenance | Acquisition maintenance | Full service | Non concerné pour l'offre</t>
+          <t>el260e dans 100-Parametres</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Identifiant écrit différemment (majuscules)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>El147</t>
+          <t>El260f</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Terme échoir | Terme échu | Multi terme (échu et échoir)</t>
+          <t>El260f dans 3-Elaboration.O, el260f dans 140-Standards</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Identifiant écrit différemment (majuscules)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>El169</t>
+          <t>El260f</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Stockage UGAP chez le titulaire (déporté vente) | Stockage UGAP au profit du titulaire (consignation) | Stockage Intermédiaire | Stockage en plateforme externalisée | Stock de consignation</t>
+          <t>el260f dans 100-Parametres</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Identifiant écrit différemment (majuscules)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>El172</t>
+          <t>El260g</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Franco France Métropolitaine | FEC (Entrepôt UGAP) | Départ Usine | Franco France Continentale</t>
+          <t>El260g dans 3-Elaboration.O, el260g dans 140-Standards</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Identifiant écrit différemment (majuscules)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>El173</t>
+          <t>El260h</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Chez le transitaire du bénéficiaire en France Métropolitaine | Sur le site du bénéficiaire avec prise en charge des frais d'emballage de transport et de dédouanement</t>
+          <t>El260h dans 3-Elaboration.O, el260h dans 140-Standards</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Identifiant écrit différemment (majuscules)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>El179</t>
+          <t>El260i</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Titulaire/Constructeur/Tiers</t>
+          <t>El260i dans 3-Elaboration.O, el260i dans 140-Standards</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Identifiant écrit différemment (majuscules)</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>El181b</t>
+          <t>El260i</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Sur site client | Sur les lieux d'utilisation du matériel | Sur site bénéficiaire | Sur site ou en retour atelier (frais logistiques A/R à la charge du titulaire), chez le titulaire ou tiers (agent, …</t>
+          <t>el260i dans 100-Parametres</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Identifiant écrit différemment (majuscules)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>El182</t>
+          <t>El498</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Sous un délai de résolution fixé à 21 jours | Sous un délai de résolution fixé à 30 jours | Différent de 30 jours</t>
+          <t>El498 dans 3-Elaboration.O, el498 dans 140-Standards</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>El205</t>
+          <t>El102</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Critères prévus dans le cadre de l’analyse multicritère des offres | Définition de l’objet du (des) lot(s) et/ou éléments obligatoires du cahier des charges | Pilotage avec KPI (key performance indic…</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>El206b</t>
+          <t>El110</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Nb fichiers traçabilité traités | Délai transmission fichiers  traçabilité | Tx d prise en compte des commande | Fiabilité livraison prév. | Fiabilité date livraison prév. | Conformité facturation fo…</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>El219</t>
+          <t>El112b</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Réseau | SMAR</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>El220</t>
+          <t>El113</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Oui, surcoût outre-mer | Non, Absence de surcoût outre-mer</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>El266</t>
+          <t>El116</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Non, Pas de logiciels prévus dans les éléments concédés ou cédés | Oui, logiciesl cédés prévus | Oui, logiciels concédés prévus</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>El271</t>
+          <t>El118</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Client | Fournisseur (Web service) | UGAP</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>El271c</t>
+          <t>El120</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Stock Savigny le Temple | Stock déporté chez le fournisseur | Stock en plateforme externalisée (La Poste) | Possibilité de faire du stock de consignation chez le fournisseur</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>El29</t>
+          <t>El121</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Etat | Opérateurs de l'Etat | Etablissements Hospitaliers | Collectivités territoriales | Clients transfrontaliers | Autres</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>El30</t>
+          <t>El122</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Sociétés d’autoroutes | Délégataires de service public | Caisses et entreprises | Autre</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>El304</t>
+          <t>El125</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Définition du besoin, acceptation du devis UGAP | Emission d’une commande client et transmission des CGE | Non concerné pour l'offre</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>El305</t>
+          <t>El127</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Recueil des besoins | Remise d’un dossier technique à l’appui du devis qualification et solution technique | Non concerné pour l'offre</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>El306</t>
+          <t>El132</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Accompagnement client et réalisation devis/commande | Application du process de commande et veille à ce que celui-ci soit respecté tout au long du marché | D’une manière générale, amélioration de la …</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>El308</t>
+          <t>El136</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Référence forfaitaire petite commande | Minima de commande | Politique de remise (ex remise sur tarif public) | Barème dégressif en fonction des quantités | Conditions de livraison | surcoût (îles li…</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>El308b</t>
+          <t>El138</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Franco France Métropolitaine | FEC (Entrepôt UGAP) | Départ Usine | Franco France Continentale</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>El316</t>
+          <t>El140</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Prix fermes | Prix révisables sur tarif public à la date d'anniversaire | Prix révisables sur tarif public à tout moment | Prix révisables sur tarif public à date fixe | Prix révisables sur indice | …</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>El318</t>
+          <t>El141</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Variation taux de remise à la hausse ou à la baisse dans la limite du taux minimum indiqué en annexe à l’acte d’engagement | Variation taux de remise dans le cadre de la mise en œuvre de la révision …</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>El325</t>
+          <t>El142</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Liste de choix ou texte : Oui, application d'une clause de sauvegarde | Non, absence de clause de sauvegarde</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>El327</t>
+          <t>El143</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Prix initial | Dernier prix révisé | indice inital | dernier indice révisé</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>El332</t>
+          <t>El146</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Non, aucune période de neutralisation | Période de congés | Changement de modèle | impact industriel lourd | Autre</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>El333</t>
+          <t>El148</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Réunion de lancement avec le titulaire | Présentation synthétique de son organisation dédiée au marché | Annuaires des contacts | Formation | Information des collaborateurs de l'UGAP | Autre</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>El333b</t>
+          <t>El150</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Alimentation et ou validation du référencement | Documentation SAV | Outils | Impératifs logistiques UGAP (tracabilité…) | Eléments pour publication (ex : photo) | Aides à la commercialisation (prêt …</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>El334</t>
+          <t>El151</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Alimentation et ou validation du référencement | Documentation SAV | Outils | Impératifs logistiques UGAP (tracabilité…) | Eléments pour publication (ex : photo) | Aides à la commercialisation (prêt …</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>El335e</t>
+          <t>El151b</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : CCP-COD | CCAP sans annexe | CCAP avec annexes | CCTP | Dossier Technique | Mémoire technique du titulaire | Fiches technico-commerciale | CCF</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>El335h</t>
+          <t>El152</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Attestation d’admission par le bénéficiaire | Tableau des étendues géographiques et prestations annexes | Questionnaire relatif au besoin client | Attestation de restitution de la batterie en fin de …</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>El343</t>
+          <t>El152b</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Les îles littorales : o	Garantie contractuelle, o	Prestations incluses dans le prix du matériel de base, o	Prestations annexes non incluses dans le prix du matériel de base.</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>El343b</t>
+          <t>El153</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : DROM-COM : Garantie contractuelle | DROM-COM : Prestations incluses dans le prix du matériel de base | DROM-COM : Prestations annexes non incluses dans le prix du matériel de base.</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>El35</t>
+          <t>El155</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Print (catalogue général, catalogue spécialisé, plaquettes fournisseurs…) | Web (ugap.fr) | Animation (emailing, communiqué de presse, push…)</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>El351</t>
+          <t>El156</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : liste des principales fournitures ou services effectuées au cours des 3 dernières années | Titres d’études et professionnels de l’opérateur économique et/ou des cadres de l’entreprise, et notamment d…</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>El361</t>
+          <t>El156b</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Fiches technico-commerciales | images numériques | Publipostages | Nuanciers | Une banque de donnée de type AUTOCAD | Matériel de démonstration | Guide de vente</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>El370</t>
+          <t>El160</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : préventive | corrective/curative</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>El377</t>
+          <t>El161</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : remise en état des Matériels | remise en état des Installations et logiciels</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>El387</t>
+          <t>El161c</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : concomitant à la commande (volet 1) et à l’issue de l’admission du matériel (volet 2) | la fin de la période de garantie | la fin de la période d'extension de garantie | Autre</t>
+          <t>« Liste de choix ou texte  » → « Liste de choix ou texte »</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>El493</t>
+          <t>El162</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Mensuelle | trimestrielle | semestrielle, annuelle</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>El500c</t>
+          <t>El163c</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Représentations françaises dans l’Union Européenne | Représentations françaises à l’étranger | Monaco, Suisse, Andorre | EEE | Autres</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>El59</t>
+          <t>El163d</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : France métropolitaine | France continentale | Corse et îles littorales non desservies par un pont gratuit | DROM | COM | Etranger</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>El60b</t>
+          <t>El163e</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : France métropolitaine | France continentale | Corse et îles littorales non desservies par un pont gratuit | DROM | COM | Etranger</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>El60c</t>
+          <t>El163f</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Représentations françaises dans l’Union Européenne | Représentations françaises à l’étranger | Monaco, Suisse, Andorre | EEE | Autres</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>El73</t>
+          <t>El164</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Liste choix unique : Sur règle d’attribution définie au CCAP sur la base d’un questionnaire client ou d’une attestation de choix dérogatoire sans règle d’attribution à la défaillance, | Sur règle d’attribution définie au…</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>El78j</t>
+          <t>El164a</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Mono client | Multi client</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>El84</t>
+          <t>El167</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Liste choix unique : Oui, Le principe de reconduction s'applique | Non, dérogation au principe de reconduction</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>El92</t>
+          <t>El168</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Abandon de lots | Nouveaux lots | Evolution de format des lots reconduits</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Choix repris du texte « Choix de réponse » (pas de liste déroulante)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>El96</t>
+          <t>El173b</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Liste choix multiple : Dépendance économique | Contraintes règlementaires | Risque de conflits d'intérêt | Autre</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Identifiant écrit différemment (majuscules)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>EL492</t>
+          <t>El174</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>EL492 dans 3-Elaboration.O, El492 dans 140-Standards</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Identifiant écrit différemment (majuscules)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>El260b</t>
+          <t>El177</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>El260b dans 3-Elaboration.O, el260b dans 140-Standards</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Identifiant écrit différemment (majuscules)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>El260c</t>
+          <t>El180a</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>El260c dans 3-Elaboration.O, el260c dans 140-Standards</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Identifiant écrit différemment (majuscules)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>El260c</t>
+          <t>El183</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>el260c dans 100-Parametres</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Identifiant écrit différemment (majuscules)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>El260c</t>
+          <t>El183b</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>el260c dans 100-Parametres</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Identifiant écrit différemment (majuscules)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>El260d</t>
+          <t>El183e</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>El260d dans 3-Elaboration.O, el260d dans 140-Standards</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Identifiant écrit différemment (majuscules)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>El260d</t>
+          <t>El183g</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>el260d dans 100-Parametres</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Identifiant écrit différemment (majuscules)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>El260e</t>
+          <t>El183i</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>El260e dans 3-Elaboration.O, el260e dans 140-Standards</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Identifiant écrit différemment (majuscules)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>El260e</t>
+          <t>El183j</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>el260e dans 100-Parametres</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Identifiant écrit différemment (majuscules)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>El260f</t>
+          <t>El183l</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>El260f dans 3-Elaboration.O, el260f dans 140-Standards</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Identifiant écrit différemment (majuscules)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>El260f</t>
+          <t>El184</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>el260f dans 100-Parametres</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Identifiant écrit différemment (majuscules)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>El260g</t>
+          <t>El185</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>El260g dans 3-Elaboration.O, el260g dans 140-Standards</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Identifiant écrit différemment (majuscules)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>El260h</t>
+          <t>El186</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>El260h dans 3-Elaboration.O, el260h dans 140-Standards</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Identifiant écrit différemment (majuscules)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>El260i</t>
+          <t>El189</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>El260i dans 3-Elaboration.O, el260i dans 140-Standards</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Identifiant écrit différemment (majuscules)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>El260i</t>
+          <t>El191</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>el260i dans 100-Parametres</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Identifiant écrit différemment (majuscules)</t>
+          <t>Mode de réponse uniformisé</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>El498</t>
+          <t>El192</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>El498 dans 3-Elaboration.O, el498 dans 140-Standards</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
@@ -6999,7 +8362,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>El102</t>
+          <t>El199b</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -7016,7 +8379,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>El110</t>
+          <t>El2</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -7033,7 +8396,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>El112b</t>
+          <t>El200</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -7050,7 +8413,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>El113</t>
+          <t>El205a</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -7067,7 +8430,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>El116</t>
+          <t>El208</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -7084,7 +8447,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>El118</t>
+          <t>El210</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -7101,7 +8464,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>El120</t>
+          <t>El211</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -7118,7 +8481,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>El121</t>
+          <t>El217</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -7135,7 +8498,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>El122</t>
+          <t>El222</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -7152,7 +8515,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>El125</t>
+          <t>El223</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7169,7 +8532,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>El127</t>
+          <t>El223d</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7186,7 +8549,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>El132</t>
+          <t>El224b</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7203,7 +8566,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>El136</t>
+          <t>El224d</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7220,7 +8583,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>El138</t>
+          <t>El24</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7237,7 +8600,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>El140</t>
+          <t>El25</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7254,7 +8617,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>El141</t>
+          <t>El258</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7271,7 +8634,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>El142</t>
+          <t>El258c</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7288,7 +8651,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>El143</t>
+          <t>El258d</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7305,7 +8668,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>El146</t>
+          <t>El259</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7322,7 +8685,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>El148</t>
+          <t>El26</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7339,7 +8702,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>El150</t>
+          <t>El260e</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7356,7 +8719,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>El151</t>
+          <t>El263</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7373,7 +8736,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>El151b</t>
+          <t>El265</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7390,12 +8753,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>El152</t>
+          <t>El268</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
+          <t>« Liste de choix ou texte  » → « Liste de choix ou texte »</t>
         </is>
       </c>
     </row>
@@ -7407,7 +8770,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>El152b</t>
+          <t>El269</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7424,7 +8787,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>El153</t>
+          <t>El270</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7441,7 +8804,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>El155</t>
+          <t>El271b</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -7458,7 +8821,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>El156</t>
+          <t>El285</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -7475,7 +8838,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>El156b</t>
+          <t>El2b</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -7492,7 +8855,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>El160</t>
+          <t>El302</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -7509,7 +8872,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>El161</t>
+          <t>El303</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -7526,12 +8889,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>El161c</t>
+          <t>El307</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>« Liste de choix ou texte  » → « Liste de choix ou texte »</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
@@ -7543,7 +8906,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>El162</t>
+          <t>El308g</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -7560,7 +8923,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>El163c</t>
+          <t>El308h</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -7577,7 +8940,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>El163d</t>
+          <t>El309</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -7594,7 +8957,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>El163e</t>
+          <t>El30b</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -7611,7 +8974,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>El163f</t>
+          <t>El311</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -7628,7 +8991,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>El164</t>
+          <t>El312</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -7645,7 +9008,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>El164a</t>
+          <t>El313</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -7662,7 +9025,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>El167</t>
+          <t>El313b</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -7679,7 +9042,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>El168</t>
+          <t>El314</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -7696,7 +9059,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>El173b</t>
+          <t>El315</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -7713,7 +9076,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>El174</t>
+          <t>El315b</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -7730,7 +9093,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>El177</t>
+          <t>El317</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -7747,7 +9110,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>El180a</t>
+          <t>El317a</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -7764,7 +9127,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>El183</t>
+          <t>El318a</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -7781,7 +9144,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>El183b</t>
+          <t>El320</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -7798,7 +9161,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>El183e</t>
+          <t>El321</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -7815,7 +9178,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>El183g</t>
+          <t>El324</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -7832,12 +9195,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>El183i</t>
+          <t>El325</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
+          <t>« Liste de choix ou texte  » → « Liste de choix ou texte »</t>
         </is>
       </c>
     </row>
@@ -7849,7 +9212,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>El183j</t>
+          <t>El328</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -7866,7 +9229,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>El183l</t>
+          <t>El33</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -7883,7 +9246,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>El184</t>
+          <t>El330</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -7900,7 +9263,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>El185</t>
+          <t>El332b</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -7917,7 +9280,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>El186</t>
+          <t>El335a</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -7934,7 +9297,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>El189</t>
+          <t>El335f</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -7951,7 +9314,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>El191</t>
+          <t>El336</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -7968,7 +9331,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>El192</t>
+          <t>El337b</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -7985,7 +9348,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>El199b</t>
+          <t>El338</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -8002,7 +9365,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>El2</t>
+          <t>El339b</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -8019,7 +9382,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>El200</t>
+          <t>El339c</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -8036,7 +9399,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>El205a</t>
+          <t>El342</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -8053,7 +9416,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>El208</t>
+          <t>El344</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -8070,7 +9433,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>El210</t>
+          <t>El346</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -8087,7 +9450,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>El211</t>
+          <t>El348</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -8104,7 +9467,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>El217</t>
+          <t>El350</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -8121,7 +9484,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>El222</t>
+          <t>El352</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -8138,7 +9501,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>El223</t>
+          <t>El353</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -8155,7 +9518,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>El223d</t>
+          <t>El356</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -8172,12 +9535,12 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>El224b</t>
+          <t>El357</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
+          <t>« Texte  » → « Texte »</t>
         </is>
       </c>
     </row>
@@ -8189,7 +9552,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>El224d</t>
+          <t>El358</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -8206,7 +9569,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>El24</t>
+          <t>El359</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -8223,7 +9586,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>El25</t>
+          <t>El36</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -8240,7 +9603,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>El258</t>
+          <t>El369</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -8257,7 +9620,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>El258c</t>
+          <t>El376</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -8274,7 +9637,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>El258d</t>
+          <t>El38</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -8291,7 +9654,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>El259</t>
+          <t>El380</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -8308,7 +9671,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>El26</t>
+          <t>El381</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -8325,7 +9688,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>El260e</t>
+          <t>El391</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -8342,7 +9705,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>El263</t>
+          <t>El4</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -8359,7 +9722,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>El265</t>
+          <t>El40</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -8376,12 +9739,12 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>El268</t>
+          <t>El401</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>« Liste de choix ou texte  » → « Liste de choix ou texte »</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
@@ -8393,7 +9756,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>El269</t>
+          <t>El41</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -8410,7 +9773,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>El270</t>
+          <t>El41b</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -8427,7 +9790,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>El271b</t>
+          <t>El43</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -8444,7 +9807,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>El285</t>
+          <t>El44</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -8461,7 +9824,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>El2b</t>
+          <t>El445</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -8478,7 +9841,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>El302</t>
+          <t>El45</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -8495,7 +9858,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>El303</t>
+          <t>El46</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -8512,7 +9875,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>El307</t>
+          <t>El47</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -8529,7 +9892,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>El308g</t>
+          <t>El48</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -8546,7 +9909,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>El308h</t>
+          <t>El488</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -8563,7 +9926,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>El309</t>
+          <t>El49</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -8580,7 +9943,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>El30b</t>
+          <t>El490</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -8597,7 +9960,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>El311</t>
+          <t>El495</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -8614,7 +9977,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>El312</t>
+          <t>El496</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -8631,7 +9994,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>El313</t>
+          <t>El507</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -8648,7 +10011,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>El313b</t>
+          <t>El508</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -8665,7 +10028,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>El314</t>
+          <t>El509</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -8682,7 +10045,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>El315</t>
+          <t>El511</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -8699,12 +10062,12 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>El315b</t>
+          <t>El61</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
+          <t>« Annexe 10- Couverture géographique » → « Annexe 10 - Couverture géographique »</t>
         </is>
       </c>
     </row>
@@ -8716,7 +10079,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>El317</t>
+          <t>El62</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -8733,7 +10096,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>El317a</t>
+          <t>El63</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -8750,7 +10113,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>El318a</t>
+          <t>El69</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -8767,7 +10130,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>El320</t>
+          <t>El70</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -8784,7 +10147,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>El321</t>
+          <t>El71</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -8801,7 +10164,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>El324</t>
+          <t>El72</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -8818,12 +10181,12 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>El325</t>
+          <t>El73</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>« Liste de choix ou texte  » → « Liste de choix ou texte »</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
@@ -8835,7 +10198,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>El328</t>
+          <t>El73e</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -8852,7 +10215,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>El33</t>
+          <t>El77</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -8869,7 +10232,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>El330</t>
+          <t>El78b</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -8886,7 +10249,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>El332b</t>
+          <t>El78c</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -8903,7 +10266,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>El335a</t>
+          <t>El78e</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -8920,7 +10283,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>El335f</t>
+          <t>El78f</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -8937,7 +10300,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>El336</t>
+          <t>El78h</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -8954,7 +10317,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>El337b</t>
+          <t>El78l</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -8971,7 +10334,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>El338</t>
+          <t>El78m</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -8988,7 +10351,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>El339b</t>
+          <t>El80</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -9005,7 +10368,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>El339c</t>
+          <t>El80a</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -9022,12 +10385,12 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>El342</t>
+          <t>El81b</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
+          <t>« Liste de choix ou texte  » → « Liste de choix ou texte »</t>
         </is>
       </c>
     </row>
@@ -9039,7 +10402,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>El344</t>
+          <t>El82</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -9056,7 +10419,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>El346</t>
+          <t>El84</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -9073,7 +10436,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>El348</t>
+          <t>El85b</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -9090,7 +10453,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>El350</t>
+          <t>El86</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -9107,7 +10470,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>El352</t>
+          <t>El88</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -9124,7 +10487,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>El353</t>
+          <t>El91</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -9141,7 +10504,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>El356</t>
+          <t>El94</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -9158,12 +10521,12 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>El357</t>
+          <t>El95</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>« Texte  » → « Texte »</t>
+          <t>« Liste choix unique  » → « Liste choix unique »</t>
         </is>
       </c>
     </row>
@@ -9175,7 +10538,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>El358</t>
+          <t>El97</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -9192,7 +10555,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>El359</t>
+          <t>El99</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -9204,1052 +10567,66 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>Mode de réponse uniformisé</t>
+          <t>Niveau de standard en minuscules</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>El36</t>
+          <t>El328b</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
+          <t>« sp » → « Sp » (DAG_SOFI)</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Mode de réponse uniformisé</t>
+          <t>Niveau de standard en minuscules</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>El369</t>
+          <t>El328b</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
+          <t>« sp » → « Sp » (DS)</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>Mode de réponse uniformisé</t>
+          <t>Niveau de standard en minuscules</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>El376</t>
+          <t>El328b</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
+          <t>« sp » → « Sp » (Non_standardisé)</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>Mode de réponse uniformisé</t>
+          <t>Niveau de standard en minuscules</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>El38</t>
+          <t>El33b</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>El380</t>
-        </is>
-      </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>El381</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>El391</t>
-        </is>
-      </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>El4</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>El40</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>El401</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B217" s="2" t="inlineStr">
-        <is>
-          <t>El41</t>
-        </is>
-      </c>
-      <c r="C217" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>El41b</t>
-        </is>
-      </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t>El43</t>
-        </is>
-      </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>El44</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>El445</t>
-        </is>
-      </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>El45</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>El46</t>
-        </is>
-      </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>El47</t>
-        </is>
-      </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>El48</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>El488</t>
-        </is>
-      </c>
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>El49</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>El490</t>
-        </is>
-      </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B229" s="2" t="inlineStr">
-        <is>
-          <t>El495</t>
-        </is>
-      </c>
-      <c r="C229" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B230" s="2" t="inlineStr">
-        <is>
-          <t>El496</t>
-        </is>
-      </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B231" s="2" t="inlineStr">
-        <is>
-          <t>El507</t>
-        </is>
-      </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B232" s="2" t="inlineStr">
-        <is>
-          <t>El508</t>
-        </is>
-      </c>
-      <c r="C232" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B233" s="2" t="inlineStr">
-        <is>
-          <t>El509</t>
-        </is>
-      </c>
-      <c r="C233" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B234" s="2" t="inlineStr">
-        <is>
-          <t>El511</t>
-        </is>
-      </c>
-      <c r="C234" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B235" s="2" t="inlineStr">
-        <is>
-          <t>El61</t>
-        </is>
-      </c>
-      <c r="C235" s="2" t="inlineStr">
-        <is>
-          <t>« Annexe 10- Couverture géographique » → « Annexe 10 - Couverture géographique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B236" s="2" t="inlineStr">
-        <is>
-          <t>El62</t>
-        </is>
-      </c>
-      <c r="C236" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B237" s="2" t="inlineStr">
-        <is>
-          <t>El63</t>
-        </is>
-      </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B238" s="2" t="inlineStr">
-        <is>
-          <t>El69</t>
-        </is>
-      </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>El70</t>
-        </is>
-      </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>El71</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>El72</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B242" s="2" t="inlineStr">
-        <is>
-          <t>El73</t>
-        </is>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B243" s="2" t="inlineStr">
-        <is>
-          <t>El73e</t>
-        </is>
-      </c>
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B244" s="2" t="inlineStr">
-        <is>
-          <t>El77</t>
-        </is>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>El78b</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>El78c</t>
-        </is>
-      </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t>El78e</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>El78f</t>
-        </is>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B249" s="2" t="inlineStr">
-        <is>
-          <t>El78h</t>
-        </is>
-      </c>
-      <c r="C249" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B250" s="2" t="inlineStr">
-        <is>
-          <t>El78l</t>
-        </is>
-      </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B251" s="2" t="inlineStr">
-        <is>
-          <t>El78m</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B252" s="2" t="inlineStr">
-        <is>
-          <t>El80</t>
-        </is>
-      </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B253" s="2" t="inlineStr">
-        <is>
-          <t>El80a</t>
-        </is>
-      </c>
-      <c r="C253" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B254" s="2" t="inlineStr">
-        <is>
-          <t>El81b</t>
-        </is>
-      </c>
-      <c r="C254" s="2" t="inlineStr">
-        <is>
-          <t>« Liste de choix ou texte  » → « Liste de choix ou texte »</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B255" s="2" t="inlineStr">
-        <is>
-          <t>El82</t>
-        </is>
-      </c>
-      <c r="C255" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B256" s="2" t="inlineStr">
-        <is>
-          <t>El84</t>
-        </is>
-      </c>
-      <c r="C256" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B257" s="2" t="inlineStr">
-        <is>
-          <t>El85b</t>
-        </is>
-      </c>
-      <c r="C257" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B258" s="2" t="inlineStr">
-        <is>
-          <t>El86</t>
-        </is>
-      </c>
-      <c r="C258" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B259" s="2" t="inlineStr">
-        <is>
-          <t>El88</t>
-        </is>
-      </c>
-      <c r="C259" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B260" s="2" t="inlineStr">
-        <is>
-          <t>El91</t>
-        </is>
-      </c>
-      <c r="C260" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B261" s="2" t="inlineStr">
-        <is>
-          <t>El94</t>
-        </is>
-      </c>
-      <c r="C261" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B262" s="2" t="inlineStr">
-        <is>
-          <t>El95</t>
-        </is>
-      </c>
-      <c r="C262" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B263" s="2" t="inlineStr">
-        <is>
-          <t>El97</t>
-        </is>
-      </c>
-      <c r="C263" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="2" t="inlineStr">
-        <is>
-          <t>Mode de réponse uniformisé</t>
-        </is>
-      </c>
-      <c r="B264" s="2" t="inlineStr">
-        <is>
-          <t>El99</t>
-        </is>
-      </c>
-      <c r="C264" s="2" t="inlineStr">
-        <is>
-          <t>« Liste choix unique  » → « Liste choix unique »</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="2" t="inlineStr">
-        <is>
-          <t>Niveau de standard en minuscules</t>
-        </is>
-      </c>
-      <c r="B265" s="2" t="inlineStr">
-        <is>
-          <t>El328b</t>
-        </is>
-      </c>
-      <c r="C265" s="2" t="inlineStr">
-        <is>
-          <t>« sp » → « Sp » (DAG_SOFI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="2" t="inlineStr">
-        <is>
-          <t>Niveau de standard en minuscules</t>
-        </is>
-      </c>
-      <c r="B266" s="2" t="inlineStr">
-        <is>
-          <t>El328b</t>
-        </is>
-      </c>
-      <c r="C266" s="2" t="inlineStr">
-        <is>
-          <t>« sp » → « Sp » (DS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="2" t="inlineStr">
-        <is>
-          <t>Niveau de standard en minuscules</t>
-        </is>
-      </c>
-      <c r="B267" s="2" t="inlineStr">
-        <is>
-          <t>El328b</t>
-        </is>
-      </c>
-      <c r="C267" s="2" t="inlineStr">
-        <is>
-          <t>« sp » → « Sp » (Non_standardisé)</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="2" t="inlineStr">
-        <is>
-          <t>Niveau de standard en minuscules</t>
-        </is>
-      </c>
-      <c r="B268" s="2" t="inlineStr">
-        <is>
-          <t>El33b</t>
-        </is>
-      </c>
-      <c r="C268" s="2" t="inlineStr">
         <is>
           <t>« sp » → « Sp » (DAV)</t>
         </is>
